--- a/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>TTC</t>
   </si>
@@ -656,408 +656,434 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45324</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45051</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44960</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44771</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44680</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44589</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44407</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44225</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43952</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43679</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43588</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43497</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43315</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43224</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43133</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42860</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1001900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>983300</v>
+      </c>
+      <c r="F8" s="3">
         <v>1081800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1339300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1148800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1172000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1160600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1249500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>932700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>960700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>976800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1149100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>873000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>841000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>841000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>929400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>767500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>734400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>838700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>962000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>603000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>539300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>655800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>875300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>548200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>488600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>627900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>872800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>515800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>468400</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>657400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>653600</v>
+      </c>
+      <c r="F9" s="3">
         <v>709400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>859600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>752900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>773100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>760600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>844100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>632200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>671300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>645700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>746200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>558000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>540600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>546400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>622700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>479400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>489300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>572700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>640700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>387300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>360200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>422200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>551200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>344000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>304400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>401200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>556500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>322400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>344500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>329700</v>
+      </c>
+      <c r="F10" s="3">
         <v>372400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>479700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>395900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>398900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>400000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>405400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>300500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>289400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>331100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>402900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>315100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>300400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>294600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>306700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>288100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>245100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>266000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>321300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>215700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>179100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>233600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>324100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>204200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>184200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>226700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>316300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>193400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>172200</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1115,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1178,8 +1206,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1267,19 +1301,25 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>151300</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1290,33 +1330,33 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>5800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-17100</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1356,8 +1396,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1445,8 +1491,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1475,186 +1527,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>913300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>888700</v>
+      </c>
+      <c r="F17" s="3">
         <v>1100900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1120500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1012400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1021600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>997500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1078900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>841000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>886500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>854900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>968400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>731500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>747500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>725000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>803600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>676400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>691100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>764800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>824300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>532900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>496300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>562900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>705000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>481300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>441200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>540200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>713500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>455300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>424800</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>94600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-19100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>218800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>136400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>150400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>163100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>170600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>91700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>74200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>121900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>180700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>141500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>93500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>116000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>125800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>91100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>43300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>73900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>137700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>70100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>43000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>92900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>170300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>66900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>47400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>87700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>159300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>60500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1686,453 +1752,485 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F20" s="3">
         <v>5500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>6800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>9100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>3100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>4200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>3100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>8800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>6300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>6200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>4700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>5500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>5100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>3600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>4300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>4300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>5400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>3700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>3900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>137600</v>
+      </c>
+      <c r="F21" s="3">
         <v>13700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>253400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>173700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>184600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>192400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>201100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>119100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>102800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>148100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>209500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>167400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>122400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>143600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>152800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>117100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>77400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>99200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>171700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>90300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>67800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>109700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>188800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>86400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>69000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>106300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>181000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>81000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F22" s="3">
         <v>15000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>14700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>14100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>11500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>9200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>8000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>7000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>7000</v>
       </c>
       <c r="L22" s="3">
         <v>7000</v>
       </c>
       <c r="M22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="O22" s="3">
         <v>7100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>7500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>8000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>8300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>8700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>8200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>8400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>9000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>6700</v>
-      </c>
-      <c r="V22" s="3">
-        <v>4700</v>
-      </c>
-      <c r="W22" s="3">
-        <v>4900</v>
       </c>
       <c r="X22" s="3">
         <v>4700</v>
       </c>
       <c r="Y22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Z22" s="3">
         <v>4700</v>
       </c>
-      <c r="Z22" s="3">
-        <v>4800</v>
-      </c>
       <c r="AA22" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="AB22" s="3">
         <v>4800</v>
       </c>
       <c r="AC22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE22" s="3">
         <v>4700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>4900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>86900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-28600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>210800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>131300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>143300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>157100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>165100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>87100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>69300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>117500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>177200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>135800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>88600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>111000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>121400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>86100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>43700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>71200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>137200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>70000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>43600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>93300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>169200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>66400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>46900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>88400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>158300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>59600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F24" s="3">
         <v>-13600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>43400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>24500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>25700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>31900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>33900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>17600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>9200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>21100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>35100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>24500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>16400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>22000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>22900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>16000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>11600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>21600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>10500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>4400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>14800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>37900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>10700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>13100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>20000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>37800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>14600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2220,186 +2318,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>70300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-15000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>167500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>106900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>117600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>125200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>131100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>69500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>60100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>96300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>142200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>111300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>72200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>89000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>98400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>70100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>38200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>59700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>115600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>59500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>39100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>78500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>131300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>55700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>33800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>68400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>120500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>45000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>70300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-15000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>167500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>106900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>117600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>125200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>131100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>69500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>60100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>96300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>142200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>111300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>72200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>89000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>98400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>70100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>38200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>59700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>115600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>59500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>39100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>78500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>131300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>55700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>33800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>68400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>120500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>45000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2487,8 +2603,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2519,11 +2641,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
@@ -2537,35 +2659,35 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>900</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>500</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-33100</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2576,8 +2698,14 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2665,8 +2793,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2754,186 +2888,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-5500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-6800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-9100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-3100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-4200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-3100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-8800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-6300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-6200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-4700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-5500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>70300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-15000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>167500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>106900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>117600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>125200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>131100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>69500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>60100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>96300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>142200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>111300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>72200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>89000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>98400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>70100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>38300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>60600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>115600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>59500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>39000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>79000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>131300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>22600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>33800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>68400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>120500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>45000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3021,191 +3173,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>70300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-15000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>167500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>106900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>117600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>125200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>131100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>69500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>60100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>96300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>142200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>111300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>72200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>89000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>98400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>70100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>38300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>60600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>115600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>59500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>39000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>79000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>131300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>22600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>33800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>68400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>120500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>45000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45324</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45051</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44960</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44771</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44680</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44589</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44407</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44225</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43952</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43679</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43588</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43497</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43315</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43224</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43133</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42860</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3237,8 +3407,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3270,97 +3442,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>198500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>193100</v>
+      </c>
+      <c r="F41" s="3">
         <v>147900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>151300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>174000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>188300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>231600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>263200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>193000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>405600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>535300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>497600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>433400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>479900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>394100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>200000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>108900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>151800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>143300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>180100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>250000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>289100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>250900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>206100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>219700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>310300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>335000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>265200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>158900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>273600</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3448,417 +3628,447 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>489100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>407400</v>
+      </c>
+      <c r="F43" s="3">
         <v>390700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>462000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>377300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>332700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>350700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>439300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>366300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>310300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>301200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>391200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>306900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>261100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>294700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>400400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>321200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>268800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>312200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>428600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>225500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>193200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>219500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>329600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>198700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>183100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>221600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>328500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>183900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>326500</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1177100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1087800</v>
+      </c>
+      <c r="F44" s="3">
         <v>1112700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1127500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1131400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1051100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>939300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>891700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>832100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>738200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>665600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>628800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>675300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>652400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>656200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>714200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>739000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>651700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>620600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>611300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>416700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>358300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>364500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>394800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>439300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>329000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>349000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>341600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>402100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>110500</v>
+      </c>
+      <c r="F45" s="3">
         <v>80500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>86100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>75000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>103300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>82900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>69400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>46000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>35100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>43600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>41800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>41200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>34200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>39200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>59900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>51400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>50600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>54200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>50300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>41800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>54100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>38200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>47800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>43000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>37600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>42600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>41300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>36500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1966500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1798800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1731800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1826800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1757700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1675400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1604400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1663700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1437300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1489200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1545800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1559500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1456700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1427600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1384200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1374600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1220500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1122900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1130400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1270300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>933900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>894600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>873000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>978200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>900800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>859900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>948100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>976600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>781300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>50600</v>
+      </c>
+      <c r="F47" s="3">
         <v>48500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>53200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>45700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>39300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>31400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>30900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>24100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>20700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>19300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>25300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>23000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>19700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>22600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>27800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>25300</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
@@ -3872,11 +4082,11 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3893,186 +4103,204 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>761000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>767000</v>
+      </c>
+      <c r="F48" s="3">
         <v>741600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>677600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>658700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>647800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>605200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>588000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>585900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>554700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>529200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>527300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>532600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>546700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>539500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>537900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>504400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>437300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>426400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>425400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>279300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>271500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>249500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>245300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>234400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>235200</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>226900</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>224300</v>
       </c>
       <c r="AD48" s="3">
         <v>226900</v>
       </c>
       <c r="AE48" s="3">
+        <v>224300</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>226900</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1060100</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>982700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>990900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1000500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1153000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1161600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1169100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1178900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1170900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1177700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>841700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>848500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>855200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>832800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>832400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>837500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>844100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>709800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>714600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>700400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>705500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>331100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>330900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>333100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>335400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>308300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>308800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>308900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>310200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>312000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>302900</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4160,8 +4388,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4249,97 +4483,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F52" s="3">
         <v>63500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>30700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>31200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>24400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>20100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>25900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>28100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>29800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>25300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>28800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>30100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>26800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>30000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>27200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>31600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>55700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>52500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>64800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>78500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>73900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>79200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>76700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>73200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>89900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>85500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>87700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>82700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>80700</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4427,97 +4673,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3801100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3644300</v>
+      </c>
+      <c r="F54" s="3">
         <v>3585900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3741400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3654900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3556000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3439900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3479300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3253000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2936100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2968000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2996100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2875100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2853200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2813900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2811500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2491600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2330500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2309700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2466000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1622800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1571000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1534800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1635700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1516800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1493800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1569500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1598800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1402900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1384600</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4549,8 +4807,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4582,542 +4842,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>421800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>430000</v>
+      </c>
+      <c r="F57" s="3">
         <v>407400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>514800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>475200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>578600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>487000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>566800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>474500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>503100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>411400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>421700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>364400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>364000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>268700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>327400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>348000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>319200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>304700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>391700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>281500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>256600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>229000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>303900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>266600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>211800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>211500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>273600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>232400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
+        <v>6800</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>65000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>100000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>100000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>104200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>100000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>10000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>99900</v>
-      </c>
-      <c r="P58" s="3">
-        <v>108900</v>
       </c>
       <c r="Q58" s="3">
         <v>99900</v>
       </c>
       <c r="R58" s="3">
+        <v>108900</v>
+      </c>
+      <c r="S58" s="3">
+        <v>99900</v>
+      </c>
+      <c r="T58" s="3">
         <v>113900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>79900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>99900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>90000</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>13000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>13000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>26300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>23100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>23900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>23000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>493300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>518600</v>
+      </c>
+      <c r="F59" s="3">
         <v>500100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>509200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>512800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>485000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>459200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>444000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>411600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>433900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>442800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>467200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>445200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>392000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>419500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>428500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>362400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>357800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>351900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>360100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>283500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>276100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>282600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>335500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>292900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>283800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>309400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>324900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>263700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>479800</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>921900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>948600</v>
+      </c>
+      <c r="F60" s="3">
         <v>907500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1024000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>988000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1063600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1011300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1110700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>986100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>937000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>958400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>988900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>819500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>855800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>797100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>855700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>824300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>757000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>756400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>841800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>565000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>532600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>511700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>652400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>572500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>521800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>543900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>622400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>519100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>463800</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1179800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1031500</v>
+      </c>
+      <c r="F61" s="3">
         <v>1061300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1041200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1091000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>990800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>990600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>991000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>991400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>691200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>587300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>591500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>691400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>691300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>782000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>790900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>601000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>620900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>620800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>721100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>312600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>312500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>312500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>299300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>302500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>305600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>308800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>312000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>315300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>328500</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>153300</v>
+      </c>
+      <c r="F62" s="3">
         <v>140000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>116200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>131800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>149900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>151500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>154100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>156100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>156700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>185100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>186300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>184500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>191400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>180700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>179900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>154200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>93100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>88700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>97900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>50900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>56900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>60400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>60700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>61100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>49300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>56900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>56600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>55400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5205,8 +5503,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5294,8 +5598,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5383,97 +5693,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2253200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2133400</v>
+      </c>
+      <c r="F66" s="3">
         <v>2108800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2181400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2210800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2204300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2153300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2255800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2133500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1785000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1730900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1766700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1695400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1738400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1759800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1826500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1579600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1471000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1465900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1660700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>928400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>902100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>884500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1012400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>936000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>876700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>909600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>991000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>889900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>834500</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5505,8 +5827,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5594,8 +5918,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5683,8 +6013,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5772,8 +6108,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5861,97 +6203,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1478900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1444100</v>
+      </c>
+      <c r="F72" s="3">
         <v>1403800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1485000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1368500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1280900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1213600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1146800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1040600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1071900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1157400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1151800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1104300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1041500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>981300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>911500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>837200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>784900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>763900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>724000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>613200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>587300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>568400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>538500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>490400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>534300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>578600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>535600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>443600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>480000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6039,8 +6393,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6128,8 +6488,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6217,97 +6583,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1547900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1510900</v>
+      </c>
+      <c r="F76" s="3">
         <v>1477100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1560000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1444200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1351700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1286600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1223500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1119500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1151100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1237200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1229400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1179700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1114800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1054000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>985000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>912100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>859600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>843800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>805300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>694400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>668900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>650200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>623300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>580800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>617100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>659900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>607800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>513000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6395,191 +6773,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45324</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45051</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44960</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44771</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44680</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44589</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44407</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44225</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43952</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43679</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43588</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43497</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43315</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43224</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43133</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42860</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>70300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-15000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>167500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>106900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>117600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>125200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>131100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>69500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>60100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>96300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>142200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>111300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>72200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>89000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>98400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>70100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>38300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>60600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>115600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>59500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>39000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>79000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>131300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>22600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>33800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>68400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>120500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>45000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6611,97 +7007,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>35800</v>
+      </c>
+      <c r="F83" s="3">
         <v>27200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>27900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>28300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>29800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>26100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>28000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>24900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>26500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>23600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>25100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>24100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>25800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>24300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>22800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>22800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>25300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>19000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>27900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>15600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>19400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>11800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>14900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>15200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>17300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>13200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>18000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>16500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6789,8 +7193,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6878,8 +7288,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6967,8 +7383,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7056,8 +7478,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7145,97 +7573,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-92200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>152100</v>
+      </c>
+      <c r="F89" s="3">
         <v>93000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>130500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-68800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>142600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>111700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>132900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-90000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>78300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>158500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>223600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>95000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>233500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>235000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>94200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-23300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>78300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>95100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>138000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>26000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>105400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>120900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>130300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>8100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>84100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>106200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>155000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>15400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>80300</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7267,97 +7707,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-35600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-40700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-29300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-67700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-47000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-24100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-11900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-56100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-22000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-15700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-10500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-31400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-15300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-11800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-36100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-23400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-19200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-14200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-38200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-24600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-21700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-32900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-32200</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7445,8 +7893,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7534,97 +7988,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-56500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-40700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-22000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-67700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-41700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-25600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-413400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-57800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-21200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-47400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-31400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-151800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-11800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-28800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-18600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-698700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-26800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-38400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-22700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-56100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-10900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7656,97 +8122,105 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E96" s="3">
         <v>-35400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="G96" s="3">
         <v>-35600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-35500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-31300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-31400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-31500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-31500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-27800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-28100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-28200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-28400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-27000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-26900</v>
       </c>
       <c r="R96" s="3">
         <v>-26900</v>
       </c>
       <c r="S96" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="T96" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="U96" s="3">
         <v>-24100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-24100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-24000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-23900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-21200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-21100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-21300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-21400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-18800</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-18900</v>
       </c>
       <c r="AD96" s="3">
         <v>-19000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7834,8 +8308,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7923,8 +8403,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8012,271 +8498,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>114100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-65100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-50200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-106600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>74400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-120500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-99700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-30900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>293300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-152500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-97100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-111100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-143000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-116800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>150600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-7500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-40300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-113700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>491800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-38300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-23300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-51900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-88700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-88100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-82900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-32600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-33500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-96300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-64700</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F101" s="3">
         <v>10300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-5900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-6200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="K101" s="3">
-        <v>2200</v>
       </c>
       <c r="L101" s="3">
         <v>-2500</v>
       </c>
       <c r="M101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>3600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>4200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-5500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>7800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>1800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>45200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-22700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-14200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-43300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-31700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>70300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-212700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-129700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>37700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>64200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-46500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>85800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>194100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>91100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-42900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>8500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-36800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-69900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-39200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>38300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>44800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-90500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>69800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>106300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-114700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-3700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>TTC</t>
   </si>
@@ -656,434 +656,447 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E7" s="2">
         <v>45324</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45142</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45051</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44960</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44771</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44680</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44589</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44407</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44225</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43952</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43679</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43588</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43497</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43315</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43224</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43133</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42951</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42860</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42769</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1349000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1001900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>983300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1081800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1339300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1148800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1172000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1160600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1249500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>932700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>960700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>976800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1149100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>873000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>841000</v>
       </c>
       <c r="R8" s="3">
         <v>841000</v>
       </c>
       <c r="S8" s="3">
+        <v>841000</v>
+      </c>
+      <c r="T8" s="3">
         <v>929400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>767500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>734400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>838700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>962000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>603000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>539300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>655800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>875300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>548200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>488600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>627900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>872800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>515800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>468400</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>896000</v>
+      </c>
+      <c r="E9" s="3">
         <v>657400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>653600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>709400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>859600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>752900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>773100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>760600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>844100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>632200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>671300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>645700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>746200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>558000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>540600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>546400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>622700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>479400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>489300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>572700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>640700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>387300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>360200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>422200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>551200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>344000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>304400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>401200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>556500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>322400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>453000</v>
+      </c>
+      <c r="E10" s="3">
         <v>344500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>329700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>372400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>479700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>395900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>398900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>405400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>289400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>331100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>402900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>315100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>300400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>294600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>306700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>288100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>245100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>266000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>321300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>215700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>179100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>233600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>324100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>204200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>184200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>226700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>316300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>193400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>172200</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1117,8 +1130,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1212,8 +1226,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1307,22 +1324,25 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>151300</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1336,29 +1356,29 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>5800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-17100</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1402,8 +1422,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1497,8 +1520,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1529,198 +1555,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1161400</v>
+      </c>
+      <c r="E17" s="3">
         <v>913300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>888700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1100900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1120500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1012400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1021600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>997500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1078900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>841000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>886500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>854900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>968400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>731500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>747500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>725000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>803600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>676400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>691100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>764800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>824300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>532900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>496300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>562900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>705000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>481300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>441200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>540200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>713500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>455300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>424800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>187600</v>
+      </c>
+      <c r="E18" s="3">
         <v>88600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>94600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>218800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>136400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>150400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>163100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>170600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>91700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>74200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>121900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>180700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>141500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>93500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>116000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>125800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>91100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>73900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>137700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>70100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>43000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>92900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>170300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>66900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>47400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>87700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>159300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>60500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1754,227 +1787,234 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E20" s="3">
         <v>7700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>2500</v>
       </c>
       <c r="L20" s="3">
         <v>2500</v>
       </c>
       <c r="M20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3600</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>4300</v>
       </c>
       <c r="AC20" s="3">
         <v>4300</v>
       </c>
       <c r="AD20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AE20" s="3">
         <v>5400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>226100</v>
+      </c>
+      <c r="E21" s="3">
         <v>127000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>137600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>253400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>173700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>184600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>192400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>201100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>119100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>102800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>148100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>209500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>167400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>122400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>143600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>152800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>117100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>77400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>99200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>171700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>90300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>67800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>109700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>188800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>86400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>69000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>106300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>181000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>81000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E22" s="3">
         <v>16200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>7000</v>
       </c>
       <c r="M22" s="3">
         <v>7000</v>
@@ -1983,46 +2023,46 @@
         <v>7000</v>
       </c>
       <c r="O22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P22" s="3">
         <v>7100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4900</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>4700</v>
       </c>
       <c r="AA22" s="3">
         <v>4700</v>
       </c>
       <c r="AB22" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="AC22" s="3">
         <v>4800</v>
@@ -2031,206 +2071,215 @@
         <v>4800</v>
       </c>
       <c r="AE22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF22" s="3">
         <v>4700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>179200</v>
+      </c>
+      <c r="E23" s="3">
         <v>80100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>86900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>210800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>131300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>143300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>157100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>165100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>87100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>69300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>117500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>177200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>135800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>88600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>111000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>121400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>86100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>43700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>71200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>137200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>70000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>43600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>93300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>169200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>66400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>46900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>88400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>158300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>59600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E24" s="3">
         <v>15200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-13600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>43400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>31900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>21100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>35100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>16400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>22000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>22900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>37900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>20000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>37800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>14600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2324,198 +2373,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E26" s="3">
         <v>64900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>70300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>167500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>106900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>117600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>125200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>131100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>69500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>60100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>96300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>142200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>111300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>72200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>89000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>98400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>70100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>38200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>59700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>115600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>59500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>39100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>78500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>131300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>55700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>33800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>68400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>120500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>45000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E27" s="3">
         <v>64900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>70300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>167500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>106900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>117600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>125200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>131100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>69500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>60100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>96300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>142200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>111300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>72200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>89000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>98400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>70100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>38200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>59700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>115600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>59500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>39100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>78500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>131300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>55700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>33800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>68400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>120500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>45000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2609,8 +2667,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2647,8 +2708,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2665,32 +2726,32 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>900</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>500</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-33100</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2704,8 +2765,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2799,8 +2863,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2894,198 +2961,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-2500</v>
       </c>
       <c r="L32" s="3">
         <v>-2500</v>
       </c>
       <c r="M32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-4300</v>
       </c>
       <c r="AC32" s="3">
         <v>-4300</v>
       </c>
       <c r="AD32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E33" s="3">
         <v>64900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>70300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>167500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>106900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>117600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>125200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>131100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>69500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>60100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>96300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>142200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>111300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>72200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>89000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>98400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>70100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>38300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>60600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>115600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>59500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>39000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>79000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>131300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>22600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>33800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>68400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>120500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>45000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3179,203 +3255,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E35" s="3">
         <v>64900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>70300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>167500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>106900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>117600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>125200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>131100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>69500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>60100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>96300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>142200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>111300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>72200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>89000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>98400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>70100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>38300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>60600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>115600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>59500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>39000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>79000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>131300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>22600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>33800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>68400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>120500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>45000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E38" s="2">
         <v>45324</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45142</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45051</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44960</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44771</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44680</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44589</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44407</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44225</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43952</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43679</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43588</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43497</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43315</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43224</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43133</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42951</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42860</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42769</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3409,8 +3494,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3444,103 +3530,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>188800</v>
+      </c>
+      <c r="E41" s="3">
         <v>198500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>193100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>147900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>151300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>174000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>188300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>231600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>263200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>193000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>405600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>535300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>497600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>433400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>479900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>394100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>108900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>151800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>143300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>180100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>250000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>289100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>250900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>206100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>219700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>310300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>335000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>265200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>158900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>273600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3634,444 +3724,459 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>623100</v>
+      </c>
+      <c r="E43" s="3">
         <v>489100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>407400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>390700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>462000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>377300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>332700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>350700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>439300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>366300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>310300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>301200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>391200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>306900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>261100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>294700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>400400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>321200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>268800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>312200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>428600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>225500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>193200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>219500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>329600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>198700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>183100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>221600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>328500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>183900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>326500</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1105000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1177100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1087800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1112700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1127500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1131400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1051100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>939300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>891700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>832100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>738200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>665600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>628800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>675300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>652400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>656200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>714200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>739000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>651700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>620600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>611300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>416700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>358300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>364500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>394800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>439300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>329000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>349000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>341600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>402100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E45" s="3">
         <v>101800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>110500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>80500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>86100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>75000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>103300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>82900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>69400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>46000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>41800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>41200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>59900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>50600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>54200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>50300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>41800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>54100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>38200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>47800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>43000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>37600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>42600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>41300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2019200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1966500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1798800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1731800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1826800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1757700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1675400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1604400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1663700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1437300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1489200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1545800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1559500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1456700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1427600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1384200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1374600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1220500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1122900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1130400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1270300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>933900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>894600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>873000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>978200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>900800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>859900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>948100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>976600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>781300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E47" s="3">
         <v>48400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>50600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>53200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>45700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>39300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>31400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>30900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>24100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>19300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>25300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>23000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>19700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>22600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>27800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>25300</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>8</v>
@@ -4088,8 +4193,8 @@
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -4109,198 +4214,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>755100</v>
+      </c>
+      <c r="E48" s="3">
         <v>761000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>767000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>741600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>677600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>658700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>647800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>605200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>588000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>585900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>554700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>529200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>527300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>532600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>546700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>539500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>537900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>504400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>437300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>426400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>425400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>279300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>271500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>249500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>245300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>234400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>235200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>226900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>224300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>226900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1060100</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>973400</v>
+      </c>
+      <c r="E49" s="3">
         <v>982700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>990900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1000500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1153000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1161600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1169100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1178900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1170900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1177700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>841700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>848500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>855200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>832800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>832400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>837500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>844100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>709800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>714600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>700400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>705500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>331100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>330900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>333100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>335400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>308300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>308800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>308900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>310200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>312000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>302900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4394,8 +4508,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4489,103 +4606,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E52" s="3">
         <v>42500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>37000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>27200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>55700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>52500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>64800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>78500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>73900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>79200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>76700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>73200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>89900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>85500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>87700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>82700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>80700</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4679,103 +4802,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3852200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3801100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3644300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3585900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3741400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3654900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3556000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3439900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3479300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3253000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2936100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2968000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2996100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2875100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2853200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2813900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2811500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2491600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2330500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2309700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2466000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1622800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1571000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1534800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1635700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1516800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1493800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1569500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1598800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1402900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1384600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4809,8 +4938,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4844,169 +4974,173 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>512400</v>
+      </c>
+      <c r="E57" s="3">
         <v>421800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>430000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>407400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>514800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>475200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>578600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>487000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>566800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>474500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>503100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>411400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>421700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>364400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>364000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>268700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>327400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>348000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>319200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>304700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>391700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>281500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>256600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>229000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>303900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>266600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>211800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>211500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>273600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>232400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E58" s="3">
         <v>6800</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>65000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>100000</v>
       </c>
       <c r="L58" s="3">
         <v>100000</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>104200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>100000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>99900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>108900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>99900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>113900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>79900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>99900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>90000</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
@@ -5014,408 +5148,423 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
         <v>13000</v>
       </c>
       <c r="AC58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AD58" s="3">
         <v>26300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>23100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>23900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>23000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>522800</v>
+      </c>
+      <c r="E59" s="3">
         <v>493300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>518600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>509200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>512800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>485000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>459200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>444000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>411600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>433900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>442800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>467200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>445200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>392000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>419500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>428500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>362400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>357800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>351900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>360100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>283500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>276100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>282600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>335500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>292900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>283800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>309400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>324900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>263700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>479800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1048700</v>
+      </c>
+      <c r="E60" s="3">
         <v>921900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>948600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>907500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1024000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>988000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1063600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1011300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1110700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>986100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>937000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>958400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>988900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>819500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>855800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>797100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>855700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>824300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>757000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>756400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>841800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>565000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>532600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>511700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>652400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>572500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>521800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>543900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>622400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>519100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>463800</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1003300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1179800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1031500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1061300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1041200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1091000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>990800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>990600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>991000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>991400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>691200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>587300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>591500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>691400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>691300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>782000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>790900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>601000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>620900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>620800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>721100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>312600</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>312500</v>
       </c>
       <c r="Z61" s="3">
         <v>312500</v>
       </c>
       <c r="AA61" s="3">
+        <v>312500</v>
+      </c>
+      <c r="AB61" s="3">
         <v>299300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>302500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>305600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>308800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>312000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>315300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>328500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>148800</v>
+      </c>
+      <c r="E62" s="3">
         <v>151500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>153300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>140000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>116200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>131800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>149900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>151500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>154100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>156100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>156700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>185100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>186300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>184500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>191400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>180700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>179900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>154200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>93100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>88700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>97900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>50900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>56900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>60400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>60700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>61100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>49300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>56900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>56600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>55400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5509,8 +5658,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5604,8 +5756,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5699,103 +5854,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2253200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2133400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2108800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2181400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2210800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2204300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2153300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2255800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2133500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1785000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1730900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1766700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1695400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1738400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1759800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1826500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1579600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1471000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1465900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1660700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>928400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>902100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>884500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1012400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>936000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>876700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>909600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>991000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>889900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>834500</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5829,8 +5990,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5924,8 +6086,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6019,8 +6184,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6114,8 +6282,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6209,103 +6380,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1583200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1478900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1444100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1403800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1485000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1368500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1280900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1213600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1146800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1040600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1071900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1157400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1151800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1104300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1041500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>981300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>911500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>837200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>784900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>763900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>724000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>613200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>587300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>568400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>538500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>490400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>534300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>578600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>535600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>443600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>480000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6399,8 +6576,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6494,8 +6674,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6589,103 +6772,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1651400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1547900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1510900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1477100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1560000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1444200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1351700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1286600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1223500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1119500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1151100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1237200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1229400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1179700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1114800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1054000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>985000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>912100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>859600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>843800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>805300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>694400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>668900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>650200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>623300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>580800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>617100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>659900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>607800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>513000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6779,203 +6968,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E80" s="2">
         <v>45324</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45142</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45051</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44960</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44771</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44680</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44589</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44407</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44225</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43952</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43679</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43588</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43497</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43315</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43224</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43133</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42951</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42860</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42769</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E81" s="3">
         <v>64900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>70300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>167500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>106900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>117600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>125200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>131100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>69500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>60100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>96300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>142200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>111300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>72200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>89000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>98400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>70100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>38300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>60600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>115600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>59500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>39000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>79000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>131300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>22600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>33800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>68400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>120500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>45000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7009,103 +7207,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E83" s="3">
         <v>30700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>35800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>27900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>28300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>28000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>22800</v>
       </c>
       <c r="T83" s="3">
         <v>22800</v>
       </c>
       <c r="U83" s="3">
+        <v>22800</v>
+      </c>
+      <c r="V83" s="3">
         <v>25300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>19000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>27900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>15600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>19400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>14900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>17300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>18000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>16500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7199,8 +7401,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7294,8 +7499,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7389,8 +7597,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7484,8 +7695,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7579,103 +7793,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-92200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>152100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>93000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>130500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-68800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>142600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>111700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>132900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-90000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>78300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>158500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>223600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>95000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>233500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>235000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>94200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-23300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>78300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>95100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>138000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>26000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>105400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>120900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>130300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>84100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>106200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>155000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>15400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>80300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7709,103 +7929,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-29300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-24100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-56100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-23400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-38200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-21700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-32900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-32200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7899,8 +8123,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7994,103 +8221,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-67700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-41700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-413400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-57800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-47400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-31400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-21100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-151800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-28800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-698700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-26800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8124,55 +8357,56 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-37600</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-35400</v>
       </c>
       <c r="F96" s="3">
         <v>-35400</v>
       </c>
       <c r="G96" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="H96" s="3">
         <v>-35600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-35500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-31300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-31400</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-31500</v>
       </c>
       <c r="L96" s="3">
         <v>-31500</v>
       </c>
       <c r="M96" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="N96" s="3">
         <v>-27800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-28100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-28200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-27000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-26900</v>
       </c>
       <c r="S96" s="3">
         <v>-26900</v>
@@ -8181,46 +8415,49 @@
         <v>-26900</v>
       </c>
       <c r="U96" s="3">
-        <v>-24100</v>
+        <v>-26900</v>
       </c>
       <c r="V96" s="3">
         <v>-24100</v>
       </c>
       <c r="W96" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="X96" s="3">
         <v>-24000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-23900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-21200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-21100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-21300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-21400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-18900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8314,8 +8551,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8409,8 +8649,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8504,289 +8747,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-217500</v>
+      </c>
+      <c r="E100" s="3">
         <v>114100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-65100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-50200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-106600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>74400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-120500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-99700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-30900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>293300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-152500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-97100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-111100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-143000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-116800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-24000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>150600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-40300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-113700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>491800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-38300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-51900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-88700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-88100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-82900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-32600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-33500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-96300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-64700</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5900</v>
-      </c>
-      <c r="H101" s="3">
-        <v>2200</v>
       </c>
       <c r="I101" s="3">
         <v>2200</v>
       </c>
       <c r="J101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>7800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E102" s="3">
         <v>5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>45200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-22700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-43300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>70300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-212700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-129700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>37700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>64200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-46500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>85800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>194100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>91100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-42900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-36800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-69900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-39200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>44800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-90500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>69800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>106300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-114700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>TTC</t>
   </si>
@@ -656,447 +656,460 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E7" s="2">
         <v>45415</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45324</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45142</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45051</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44960</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44771</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44680</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44589</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44407</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44225</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43952</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43679</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43588</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43497</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43315</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43224</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43133</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42951</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42860</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42769</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1156900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1349000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1001900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>983300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1081800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1339300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1148800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1172000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1160600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1249500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>932700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>960700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>976800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1149100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>873000</v>
-      </c>
-      <c r="R8" s="3">
-        <v>841000</v>
       </c>
       <c r="S8" s="3">
         <v>841000</v>
       </c>
       <c r="T8" s="3">
+        <v>841000</v>
+      </c>
+      <c r="U8" s="3">
         <v>929400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>767500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>734400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>838700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>962000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>603000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>539300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>655800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>875300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>548200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>488600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>627900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>872800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>515800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>468400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>754100</v>
+      </c>
+      <c r="E9" s="3">
         <v>896000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>657400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>653600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>709400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>859600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>752900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>773100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>760600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>844100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>632200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>671300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>645700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>746200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>558000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>540600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>546400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>622700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>479400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>489300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>572700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>640700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>387300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>360200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>422200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>551200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>344000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>304400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>401200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>556500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>322400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>402800</v>
+      </c>
+      <c r="E10" s="3">
         <v>453000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>344500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>329700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>372400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>479700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>395900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>398900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>400000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>405400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>300500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>289400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>331100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>402900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>315100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>294600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>306700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>288100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>245100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>266000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>321300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>215700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>179100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>233600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>324100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>204200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>184200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>226700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>316300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>193400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>172200</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1131,8 +1144,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1229,8 +1243,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1327,25 +1344,28 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>151300</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1359,29 +1379,29 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>5800</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-17100</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1425,8 +1445,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1523,8 +1546,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1556,204 +1582,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1008800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1161400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>913300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>888700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1120500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1012400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1021600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>997500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1078900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>841000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>886500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>854900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>968400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>731500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>747500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>725000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>803600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>676400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>691100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>764800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>824300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>532900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>496300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>562900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>705000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>481300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>441200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>540200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>713500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>455300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>424800</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>148100</v>
+      </c>
+      <c r="E18" s="3">
         <v>187600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>88600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>94600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>218800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>136400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>150400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>163100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>170600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>91700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>74200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>121900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>180700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>141500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>93500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>116000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>125800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>91100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>73900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>137700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>70100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>43000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>92900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>170300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>66900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>47400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>87700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>159300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>60500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1788,236 +1821,243 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E20" s="3">
         <v>8300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>2500</v>
       </c>
       <c r="M20" s="3">
         <v>2500</v>
       </c>
       <c r="N20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>8800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3600</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>4300</v>
       </c>
       <c r="AD20" s="3">
         <v>4300</v>
       </c>
       <c r="AE20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AF20" s="3">
         <v>5400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>189600</v>
+      </c>
+      <c r="E21" s="3">
         <v>226100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>127000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>137600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>253400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>173700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>184600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>192400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>201100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>119100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>102800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>148100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>209500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>167400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>122400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>143600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>152800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>117100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>77400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>99200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>171700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>90300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>67800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>109700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>188800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>86400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>69000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>106300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>181000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>81000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E22" s="3">
         <v>16700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>7000</v>
       </c>
       <c r="N22" s="3">
         <v>7000</v>
@@ -2026,46 +2066,46 @@
         <v>7000</v>
       </c>
       <c r="P22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>7100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4900</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>4700</v>
       </c>
       <c r="AB22" s="3">
         <v>4700</v>
       </c>
       <c r="AC22" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="AD22" s="3">
         <v>4800</v>
@@ -2074,212 +2114,221 @@
         <v>4800</v>
       </c>
       <c r="AF22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AG22" s="3">
         <v>4700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>144200</v>
+      </c>
+      <c r="E23" s="3">
         <v>179200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>80100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>86900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>210800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>131300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>143300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>157100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>165100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>87100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>69300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>117500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>177200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>135800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>88600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>111000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>121400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>86100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>43700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>71200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>137200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>70000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>43600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>93300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>169200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>66400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>46900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>88400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>158300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>59600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E24" s="3">
         <v>34400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>16600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-13600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>43400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>33900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>35100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>22000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>22900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>14800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>20000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>37800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>14600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2376,204 +2425,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>119300</v>
+      </c>
+      <c r="E26" s="3">
         <v>144800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>64900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>70300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>167500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>106900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>117600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>125200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>131100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>69500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>60100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>96300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>142200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>111300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>72200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>89000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>98400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>70100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>38200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>59700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>115600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>59500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>39100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>78500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>131300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>55700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>33800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>68400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>120500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>45000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>119300</v>
+      </c>
+      <c r="E27" s="3">
         <v>144800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>64900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>70300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>167500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>106900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>117600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>125200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>131100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>69500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>60100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>96300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>142200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>111300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>72200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>89000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>98400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>70100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>38200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>59700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>115600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>59500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>39100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>78500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>131300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>55700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>33800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>68400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>120500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>45000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2670,8 +2728,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2711,8 +2772,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -2729,32 +2790,32 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>900</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>500</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-33100</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2768,8 +2829,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2866,8 +2930,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2964,204 +3031,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-2500</v>
       </c>
       <c r="M32" s="3">
         <v>-2500</v>
       </c>
       <c r="N32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-8800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-4300</v>
       </c>
       <c r="AD32" s="3">
         <v>-4300</v>
       </c>
       <c r="AE32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>119300</v>
+      </c>
+      <c r="E33" s="3">
         <v>144800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>64900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>70300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>167500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>106900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>117600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>125200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>131100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>69500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>60100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>96300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>142200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>111300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>72200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>89000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>98400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>70100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>38300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>60600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>115600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>59500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>39000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>79000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>131300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>22600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>33800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>68400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>120500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>45000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3258,209 +3334,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>119300</v>
+      </c>
+      <c r="E35" s="3">
         <v>144800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>64900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>70300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>167500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>106900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>117600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>125200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>131100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>69500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>60100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>96300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>142200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>111300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>72200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>89000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>98400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>70100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>38300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>60600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>115600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>59500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>39000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>79000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>131300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>22600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>33800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>68400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>120500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>45000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E38" s="2">
         <v>45415</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45324</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45142</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45051</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44960</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44771</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44680</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44589</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44407</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44225</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43952</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43679</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43588</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43497</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43315</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43224</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43133</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42951</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42860</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42769</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3495,8 +3580,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3531,106 +3617,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>221100</v>
+      </c>
+      <c r="E41" s="3">
         <v>188800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>198500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>193100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>147900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>151300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>174000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>188300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>231600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>263200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>193000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>405600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>535300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>497600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>433400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>479900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>394100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>200000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>108900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>151800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>143300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>180100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>250000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>289100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>250900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>206100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>219700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>310300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>335000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>265200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>158900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>273600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3727,459 +3817,474 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>532300</v>
+      </c>
+      <c r="E43" s="3">
         <v>623100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>489100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>407400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>390700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>462000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>377300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>332700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>350700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>439300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>366300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>310300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>301200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>391200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>306900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>261100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>294700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>400400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>321200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>268800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>312200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>428600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>225500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>193200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>219500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>329600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>198700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>183100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>221600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>328500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>183900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>326500</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1082000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1105000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1177100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1087800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1112700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1127500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1131400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1051100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>939300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>891700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>832100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>738200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>665600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>628800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>675300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>652400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>656200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>714200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>739000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>651700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>620600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>611300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>416700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>358300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>364500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>394800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>439300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>329000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>349000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>341600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>402100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E45" s="3">
         <v>102300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>101800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>110500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>80500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>86100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>75000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>103300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>82900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>69400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>46000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>43600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>41800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>41200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>34200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>59900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>51400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>50600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>54200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>50300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>41800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>54100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>38200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>47800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>43000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>37600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>42600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>41300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>36500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1913900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2019200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1966500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1798800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1731800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1826800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1757700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1675400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1604400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1663700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1437300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1489200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1545800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1559500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1456700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1427600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1384200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1374600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1220500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1122900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1130400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1270300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>933900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>894600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>873000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>978200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>900800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>859900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>948100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>976600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>781300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E47" s="3">
         <v>51700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>48400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>50600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>48500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>53200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>30900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>19300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>25300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>23000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>19700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>22600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>27800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>25300</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>8</v>
@@ -4196,8 +4301,8 @@
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -4217,204 +4322,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>748900</v>
+      </c>
+      <c r="E48" s="3">
         <v>755100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>761000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>767000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>741600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>677600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>658700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>647800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>605200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>588000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>585900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>554700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>529200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>527300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>532600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>546700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>539500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>537900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>504400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>437300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>426400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>425400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>279300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>271500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>249500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>245300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>234400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>235200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>226900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>224300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>226900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1060100</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>962600</v>
+      </c>
+      <c r="E49" s="3">
         <v>973400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>982700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>990900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1000500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1153000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1161600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1169100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1178900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1170900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1177700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>841700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>848500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>855200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>832800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>832400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>837500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>844100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>709800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>714600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>700400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>705500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>331100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>330900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>333100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>335400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>308300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>308800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>308900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>310200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>312000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>302900</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4511,8 +4625,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4609,106 +4726,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E52" s="3">
         <v>52800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>42500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>37000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>63500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>27200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>31600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>55700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>52500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>64800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>78500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>73900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>79200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>76700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>73200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>89900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>85500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>87700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>82700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>80700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4805,106 +4928,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3731400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3852200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3801100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3644300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3585900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3741400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3654900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3556000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3439900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3479300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3253000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2936100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2968000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2996100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2875100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2853200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2813900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2811500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2491600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2330500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2309700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2466000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1622800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1571000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1534800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1635700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1516800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1493800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1569500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1598800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1402900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1384600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4939,8 +5068,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4975,175 +5105,179 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>437800</v>
+      </c>
+      <c r="E57" s="3">
         <v>512400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>421800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>430000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>407400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>514800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>475200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>578600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>487000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>566800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>474500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>503100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>411400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>421700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>364400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>364000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>268700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>327400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>348000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>319200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>304700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>391700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>281500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>256600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>229000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>303900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>266600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>211800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>211500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>273600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>232400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E58" s="3">
         <v>13500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6800</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>65000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>100000</v>
       </c>
       <c r="M58" s="3">
         <v>100000</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>104200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>100000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>99900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>108900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>99900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>113900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>79900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>99900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>90000</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
@@ -5151,420 +5285,435 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>13000</v>
       </c>
       <c r="AD58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AE58" s="3">
         <v>26300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>23100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>23900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>23000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>521300</v>
+      </c>
+      <c r="E59" s="3">
         <v>522800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>493300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>518600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>500100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>509200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>512800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>485000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>459200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>444000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>411600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>433900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>442800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>467200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>445200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>392000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>419500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>428500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>362400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>357800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>351900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>360100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>283500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>276100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>282600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>335500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>292900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>283800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>309400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>324900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>263700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>479800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>984400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1048700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>921900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>948600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>907500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1024000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>988000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1063600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1011300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1110700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>986100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>937000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>958400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>988900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>819500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>855800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>797100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>855700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>824300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>757000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>756400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>841800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>565000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>532600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>511700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>652400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>572500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>521800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>543900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>622400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>519100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>463800</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>966600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1003300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1179800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1031500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1061300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1041200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1091000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>990800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>990600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>991000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>991400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>691200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>587300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>591500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>691400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>691300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>782000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>790900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>601000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>620900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>620800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>721100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>312600</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>312500</v>
       </c>
       <c r="AA61" s="3">
         <v>312500</v>
       </c>
       <c r="AB61" s="3">
+        <v>312500</v>
+      </c>
+      <c r="AC61" s="3">
         <v>299300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>302500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>305600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>308800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>312000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>315300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>328500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E62" s="3">
         <v>148800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>151500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>153300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>140000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>116200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>131800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>149900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>151500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>154100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>156100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>156700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>185100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>186300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>184500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>191400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>180700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>179900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>154200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>93100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>88700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>97900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>50900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>56900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>60400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>60700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>61100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>49300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>56900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>56600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>55400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5661,8 +5810,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5759,8 +5911,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5857,106 +6012,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2095000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2200800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2253200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2133400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2108800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2181400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2210800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2204300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2153300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2255800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2133500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1785000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1730900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1766700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1695400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1738400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1759800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1826500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1579600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1471000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1465900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1660700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>928400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>902100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>884500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1012400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>936000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>876700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>909600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>991000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>889900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>834500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5991,8 +6152,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6089,8 +6251,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6187,8 +6352,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6285,8 +6453,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6383,106 +6554,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1576200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1583200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1478900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1444100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1403800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1485000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1368500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1280900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1213600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1146800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1040600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1071900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1157400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1151800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1104300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1041500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>981300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>911500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>837200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>784900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>763900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>724000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>613200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>587300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>568400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>538500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>490400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>534300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>578600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>535600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>443600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>480000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6579,8 +6756,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6677,8 +6857,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6775,106 +6958,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1636400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1651400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1547900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1510900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1477100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1560000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1444200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1351700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1286600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1223500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1119500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1151100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1237200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1229400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1179700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1114800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1054000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>985000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>912100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>859600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>843800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>805300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>694400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>668900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>650200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>623300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>580800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>617100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>659900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>607800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>513000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6971,209 +7160,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E80" s="2">
         <v>45415</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45324</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45142</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45051</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44960</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44771</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44680</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44589</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44407</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44225</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43952</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43679</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43588</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43497</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43315</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43224</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43133</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42951</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42860</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42769</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>119300</v>
+      </c>
+      <c r="E81" s="3">
         <v>144800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>64900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>70300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>167500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>106900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>117600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>125200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>131100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>69500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>60100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>96300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>142200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>111300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>72200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>89000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>98400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>70100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>38300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>60600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>115600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>59500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>39000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>79000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>131300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>22600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>33800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>68400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>120500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>45000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7208,106 +7406,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E83" s="3">
         <v>30200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>35800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>27200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>28300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>28000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>22800</v>
       </c>
       <c r="U83" s="3">
         <v>22800</v>
       </c>
       <c r="V83" s="3">
+        <v>22800</v>
+      </c>
+      <c r="W83" s="3">
         <v>25300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>27900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>19400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>14900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>13200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>16500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7404,8 +7606,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7502,8 +7707,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7600,8 +7808,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7698,8 +7909,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7796,106 +8010,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>194700</v>
+      </c>
+      <c r="E89" s="3">
         <v>227300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-92200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>152100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>93000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>130500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-68800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>142600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>111700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>132900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-90000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>78300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>158500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>223600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>95000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>233500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>235000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>94200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-23300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>78300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>95100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>138000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>26000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>105400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>120900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>130300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>84100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>106200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>155000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>15400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>80300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7930,106 +8150,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-43800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-35600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-40700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-29300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-67700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-47000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-24100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-56100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-23400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-21700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-32900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-32200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8126,8 +8350,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8224,106 +8451,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-38500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-40700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-67700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-41700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-413400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-57800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-21200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-47400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-31400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-21100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-151800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-18600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-698700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-26800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8358,8 +8591,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8367,49 +8601,49 @@
         <v>-37500</v>
       </c>
       <c r="E96" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="F96" s="3">
         <v>-37600</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-35400</v>
       </c>
       <c r="G96" s="3">
         <v>-35400</v>
       </c>
       <c r="H96" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="I96" s="3">
         <v>-35600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-35500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-31300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-31400</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-31500</v>
       </c>
       <c r="M96" s="3">
         <v>-31500</v>
       </c>
       <c r="N96" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="O96" s="3">
         <v>-27800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-28100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-28400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-27000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-26900</v>
       </c>
       <c r="T96" s="3">
         <v>-26900</v>
@@ -8418,46 +8652,49 @@
         <v>-26900</v>
       </c>
       <c r="V96" s="3">
-        <v>-24100</v>
+        <v>-26900</v>
       </c>
       <c r="W96" s="3">
         <v>-24100</v>
       </c>
       <c r="X96" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-23900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-21200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-21100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-21300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-21400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-18900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8554,8 +8791,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8652,8 +8892,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8750,298 +8993,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-157100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-217500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>114100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-65100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-50200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-106600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>74400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-120500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-99700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-30900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>293300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-152500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-97100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-111100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-143000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-116800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-24000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>150600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-40300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-113700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>491800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-38300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-51900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-88700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-88100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-82900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-32600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-33500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-96300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-64700</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>10300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5900</v>
-      </c>
-      <c r="I101" s="3">
-        <v>2200</v>
       </c>
       <c r="J101" s="3">
         <v>2200</v>
       </c>
       <c r="K101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-6200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>7800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>45200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-43300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>70300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-212700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-129700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>37700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>64200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-46500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>85800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>194100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>91100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-42900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-36800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-69900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-39200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>38300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>44800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-13600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-90500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>69800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>106300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-114700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>TTC</t>
   </si>
@@ -912,7 +912,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>754100</v>
+        <v>747200</v>
       </c>
       <c r="E9" s="3">
         <v>896000</v>
@@ -921,7 +921,7 @@
         <v>657400</v>
       </c>
       <c r="G9" s="3">
-        <v>653600</v>
+        <v>653700</v>
       </c>
       <c r="H9" s="3">
         <v>709400</v>
@@ -930,7 +930,7 @@
         <v>859600</v>
       </c>
       <c r="J9" s="3">
-        <v>752900</v>
+        <v>752700</v>
       </c>
       <c r="K9" s="3">
         <v>773100</v>
@@ -1013,7 +1013,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>402800</v>
+        <v>409700</v>
       </c>
       <c r="E10" s="3">
         <v>453000</v>
@@ -1022,7 +1022,7 @@
         <v>344500</v>
       </c>
       <c r="G10" s="3">
-        <v>329700</v>
+        <v>329600</v>
       </c>
       <c r="H10" s="3">
         <v>372400</v>
@@ -1031,7 +1031,7 @@
         <v>479700</v>
       </c>
       <c r="J10" s="3">
-        <v>395900</v>
+        <v>396100</v>
       </c>
       <c r="K10" s="3">
         <v>398900</v>
@@ -1159,8 +1159,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>173900</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1353,13 +1353,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+        <v>10900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3900</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1370,8 +1370,8 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3">
+        <v>700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1454,25 +1454,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>30900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>30700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>35800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>27200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>27900</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>28300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1589,25 +1589,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1008800</v>
+        <v>997900</v>
       </c>
       <c r="E17" s="3">
-        <v>1161400</v>
+        <v>1157000</v>
       </c>
       <c r="F17" s="3">
-        <v>913300</v>
+        <v>909400</v>
       </c>
       <c r="G17" s="3">
-        <v>888700</v>
+        <v>888500</v>
       </c>
       <c r="H17" s="3">
-        <v>1100900</v>
+        <v>949600</v>
       </c>
       <c r="I17" s="3">
         <v>1120500</v>
       </c>
       <c r="J17" s="3">
-        <v>1012400</v>
+        <v>1011700</v>
       </c>
       <c r="K17" s="3">
         <v>1021600</v>
@@ -1690,25 +1690,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>148100</v>
+        <v>159000</v>
       </c>
       <c r="E18" s="3">
-        <v>187600</v>
+        <v>192000</v>
       </c>
       <c r="F18" s="3">
-        <v>88600</v>
+        <v>92500</v>
       </c>
       <c r="G18" s="3">
-        <v>94600</v>
+        <v>94700</v>
       </c>
       <c r="H18" s="3">
-        <v>-19100</v>
+        <v>132200</v>
       </c>
       <c r="I18" s="3">
         <v>218800</v>
       </c>
       <c r="J18" s="3">
-        <v>136400</v>
+        <v>137100</v>
       </c>
       <c r="K18" s="3">
         <v>150400</v>
@@ -1828,25 +1828,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>10600</v>
+        <v>-10600</v>
       </c>
       <c r="E20" s="3">
-        <v>8300</v>
+        <v>-8300</v>
       </c>
       <c r="F20" s="3">
-        <v>7700</v>
+        <v>-7700</v>
       </c>
       <c r="G20" s="3">
-        <v>7200</v>
+        <v>-7100</v>
       </c>
       <c r="H20" s="3">
-        <v>5500</v>
+        <v>-5500</v>
       </c>
       <c r="I20" s="3">
-        <v>6800</v>
+        <v>-6700</v>
       </c>
       <c r="J20" s="3">
-        <v>9100</v>
+        <v>-9000</v>
       </c>
       <c r="K20" s="3">
         <v>4300</v>
@@ -1929,25 +1929,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>189600</v>
+        <v>200500</v>
       </c>
       <c r="E21" s="3">
-        <v>226100</v>
+        <v>230500</v>
       </c>
       <c r="F21" s="3">
-        <v>127000</v>
+        <v>130900</v>
       </c>
       <c r="G21" s="3">
         <v>137600</v>
       </c>
       <c r="H21" s="3">
-        <v>13700</v>
+        <v>164900</v>
       </c>
       <c r="I21" s="3">
         <v>253400</v>
       </c>
       <c r="J21" s="3">
-        <v>173700</v>
+        <v>174400</v>
       </c>
       <c r="K21" s="3">
         <v>184600</v>
@@ -2247,10 +2247,10 @@
         <v>-13600</v>
       </c>
       <c r="I24" s="3">
-        <v>43400</v>
+        <v>43300</v>
       </c>
       <c r="J24" s="3">
-        <v>24500</v>
+        <v>24400</v>
       </c>
       <c r="K24" s="3">
         <v>25700</v>
@@ -3040,25 +3040,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-10600</v>
+        <v>10600</v>
       </c>
       <c r="E32" s="3">
-        <v>-8300</v>
+        <v>8300</v>
       </c>
       <c r="F32" s="3">
-        <v>-7700</v>
+        <v>7700</v>
       </c>
       <c r="G32" s="3">
-        <v>-7200</v>
+        <v>7100</v>
       </c>
       <c r="H32" s="3">
-        <v>-5500</v>
+        <v>5500</v>
       </c>
       <c r="I32" s="3">
-        <v>-6800</v>
+        <v>6700</v>
       </c>
       <c r="J32" s="3">
-        <v>-9100</v>
+        <v>9000</v>
       </c>
       <c r="K32" s="3">
         <v>-4300</v>
@@ -4028,25 +4028,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>78500</v>
+        <v>2100</v>
       </c>
       <c r="E45" s="3">
-        <v>102300</v>
+        <v>12000</v>
       </c>
       <c r="F45" s="3">
-        <v>101800</v>
+        <v>9800</v>
       </c>
       <c r="G45" s="3">
-        <v>110500</v>
+        <v>16800</v>
       </c>
       <c r="H45" s="3">
-        <v>80500</v>
+        <v>13800</v>
       </c>
       <c r="I45" s="3">
-        <v>86100</v>
+        <v>15000</v>
       </c>
       <c r="J45" s="3">
-        <v>75000</v>
+        <v>10600</v>
       </c>
       <c r="K45" s="3">
         <v>103300</v>
@@ -4735,25 +4735,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>59600</v>
+        <v>21300</v>
       </c>
       <c r="E52" s="3">
-        <v>52800</v>
+        <v>21800</v>
       </c>
       <c r="F52" s="3">
-        <v>42500</v>
+        <v>22200</v>
       </c>
       <c r="G52" s="3">
-        <v>37000</v>
+        <v>22800</v>
       </c>
       <c r="H52" s="3">
-        <v>63500</v>
+        <v>21800</v>
       </c>
       <c r="I52" s="3">
-        <v>30700</v>
+        <v>19400</v>
       </c>
       <c r="J52" s="3">
-        <v>31200</v>
+        <v>19400</v>
       </c>
       <c r="K52" s="3">
         <v>24400</v>
@@ -5213,25 +5213,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>25300</v>
+        <v>45000</v>
       </c>
       <c r="E58" s="3">
-        <v>13500</v>
+        <v>33100</v>
       </c>
       <c r="F58" s="3">
-        <v>6800</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
+        <v>25600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>19500</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>17800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>15900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -5314,25 +5314,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>521300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>522800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>493300</v>
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G59" s="3">
-        <v>518600</v>
+        <v>148600</v>
       </c>
       <c r="H59" s="3">
-        <v>500100</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>509200</v>
+        <v>154100</v>
       </c>
       <c r="J59" s="3">
-        <v>512800</v>
+        <v>1500</v>
       </c>
       <c r="K59" s="3">
         <v>485000</v>
@@ -5516,25 +5516,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>966600</v>
+        <v>1065700</v>
       </c>
       <c r="E61" s="3">
-        <v>1003300</v>
+        <v>1106500</v>
       </c>
       <c r="F61" s="3">
-        <v>1179800</v>
+        <v>1288200</v>
       </c>
       <c r="G61" s="3">
-        <v>1031500</v>
+        <v>1143600</v>
       </c>
       <c r="H61" s="3">
-        <v>1061300</v>
+        <v>1162500</v>
       </c>
       <c r="I61" s="3">
-        <v>1041200</v>
+        <v>1099100</v>
       </c>
       <c r="J61" s="3">
-        <v>1091000</v>
+        <v>1151700</v>
       </c>
       <c r="K61" s="3">
         <v>990800</v>
@@ -5617,25 +5617,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>144000</v>
+        <v>44500</v>
       </c>
       <c r="E62" s="3">
-        <v>148800</v>
+        <v>45200</v>
       </c>
       <c r="F62" s="3">
-        <v>151500</v>
+        <v>42700</v>
       </c>
       <c r="G62" s="3">
-        <v>153300</v>
+        <v>40800</v>
       </c>
       <c r="H62" s="3">
-        <v>140000</v>
+        <v>38700</v>
       </c>
       <c r="I62" s="3">
-        <v>116200</v>
+        <v>39700</v>
       </c>
       <c r="J62" s="3">
-        <v>131800</v>
+        <v>39700</v>
       </c>
       <c r="K62" s="3">
         <v>149900</v>
@@ -7413,25 +7413,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>30900</v>
+        <v>18300</v>
       </c>
       <c r="E83" s="3">
-        <v>30200</v>
+        <v>19100</v>
       </c>
       <c r="F83" s="3">
-        <v>30700</v>
+        <v>19200</v>
       </c>
       <c r="G83" s="3">
-        <v>35800</v>
+        <v>20600</v>
       </c>
       <c r="H83" s="3">
-        <v>27200</v>
+        <v>17000</v>
       </c>
       <c r="I83" s="3">
-        <v>27900</v>
+        <v>18800</v>
       </c>
       <c r="J83" s="3">
-        <v>28300</v>
+        <v>18500</v>
       </c>
       <c r="K83" s="3">
         <v>29800</v>
@@ -8034,10 +8034,10 @@
         <v>93000</v>
       </c>
       <c r="I89" s="3">
-        <v>130500</v>
+        <v>130600</v>
       </c>
       <c r="J89" s="3">
-        <v>-68800</v>
+        <v>-68900</v>
       </c>
       <c r="K89" s="3">
         <v>142600</v>
@@ -8172,7 +8172,7 @@
         <v>-35600</v>
       </c>
       <c r="I91" s="3">
-        <v>-40700</v>
+        <v>-40800</v>
       </c>
       <c r="J91" s="3">
         <v>-29300</v>
@@ -8475,10 +8475,10 @@
         <v>-56500</v>
       </c>
       <c r="I94" s="3">
-        <v>-40700</v>
+        <v>-40800</v>
       </c>
       <c r="J94" s="3">
-        <v>-22000</v>
+        <v>-21900</v>
       </c>
       <c r="K94" s="3">
         <v>-67700</v>
@@ -8598,25 +8598,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-37500</v>
+        <v>37500</v>
       </c>
       <c r="E96" s="3">
-        <v>-37500</v>
+        <v>37500</v>
       </c>
       <c r="F96" s="3">
-        <v>-37600</v>
+        <v>37600</v>
       </c>
       <c r="G96" s="3">
-        <v>-35400</v>
+        <v>35400</v>
       </c>
       <c r="H96" s="3">
-        <v>-35400</v>
+        <v>35400</v>
       </c>
       <c r="I96" s="3">
-        <v>-35600</v>
+        <v>35600</v>
       </c>
       <c r="J96" s="3">
-        <v>-35500</v>
+        <v>35500</v>
       </c>
       <c r="K96" s="3">
         <v>-31300</v>
@@ -9103,25 +9103,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>600</v>
+        <v>10300</v>
       </c>
       <c r="E101" s="3">
-        <v>-1100</v>
+        <v>-5900</v>
       </c>
       <c r="F101" s="3">
-        <v>2600</v>
+        <v>2200</v>
       </c>
       <c r="G101" s="3">
-        <v>-3300</v>
+        <v>2300</v>
       </c>
       <c r="H101" s="3">
-        <v>10300</v>
+        <v>-2000</v>
       </c>
       <c r="I101" s="3">
-        <v>-5900</v>
+        <v>-6200</v>
       </c>
       <c r="J101" s="3">
-        <v>2200</v>
+        <v>-2500</v>
       </c>
       <c r="K101" s="3">
         <v>2200</v>

--- a/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>TTC</t>
   </si>
@@ -656,460 +656,486 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45506</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45415</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45324</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45142</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45051</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44960</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44771</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44680</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44589</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44407</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44225</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43952</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43679</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43588</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43497</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43315</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43224</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43133</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42951</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42860</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42769</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>995000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1076000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1156900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1349000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1001900</v>
       </c>
-      <c r="G8" s="3">
-        <v>983300</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>983200</v>
+      </c>
+      <c r="J8" s="3">
         <v>1081800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1339300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1148800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1172000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1160600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1249500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>932700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>960700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>976800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1149100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>873000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>841000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>841000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>929400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>767500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>734400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>838700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>962000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>603000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>539300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>655800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>875300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>548200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>488600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>627900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>872800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>515800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>468400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>655600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>733900</v>
+      </c>
+      <c r="F9" s="3">
         <v>747200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>896000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>657400</v>
       </c>
-      <c r="G9" s="3">
-        <v>653700</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>653600</v>
+      </c>
+      <c r="J9" s="3">
         <v>709400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>859600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>752700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>773100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>760600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>844100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>632200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>671300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>645700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>746200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>558000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>540600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>546400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>622700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>479400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>489300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>572700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>640700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>387300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>360200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>422200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>551200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>344000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>304400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>401200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>556500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>322400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>339400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>342100</v>
+      </c>
+      <c r="F10" s="3">
         <v>409700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>453000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>344500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>329600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>372400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>479700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>396100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>398900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>400000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>405400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>300500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>289400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>331100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>402900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>315100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>300400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>294600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>306700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>288100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>245100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>266000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>321300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>215700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>179100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>233600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>324100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>204200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>184200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>226700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>316300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>193400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>172200</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1145,28 +1171,30 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>173100</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
-        <v>173900</v>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>173900</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1246,8 +1274,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1347,68 +1381,74 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F14" s="3">
         <v>10900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>4400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>3900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3">
         <v>151300</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
-        <v>700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>700</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>5800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-17100</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
@@ -1448,38 +1488,44 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>36400</v>
+      </c>
+      <c r="F15" s="3">
         <v>30900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>30200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>30700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>35800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>27200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>27900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>28300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1549,8 +1595,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1583,210 +1635,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>897200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>985800</v>
+      </c>
+      <c r="F17" s="3">
         <v>997900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1157000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>909400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>888500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>949600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1120500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1011700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1021600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>997500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1078900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>841000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>886500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>854900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>968400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>731500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>747500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>725000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>803600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>676400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>691100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>764800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>824300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>532900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>496300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>562900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>705000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>481300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>441200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>540200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>713500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>455300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>424800</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>90200</v>
+      </c>
+      <c r="F18" s="3">
         <v>159000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>192000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>92500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>94700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>132200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>218800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>137100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>150400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>163100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>170600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>91700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>74200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>121900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>180700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>141500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>93500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>116000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>125800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>91100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>43300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>73900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>137700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>70100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>43000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>92900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>170300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>66900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>47400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>87700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>159300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>60500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1822,513 +1888,545 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-10600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-8300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-7700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-5500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-6700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-9000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>3100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>3300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>3100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>8800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>6300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>6200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>4700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>5500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>5100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>3600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>4300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>4300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>5400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>3700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>3900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>133200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>141000</v>
+      </c>
+      <c r="F21" s="3">
         <v>200500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>230500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>130900</v>
       </c>
-      <c r="G21" s="3">
-        <v>137600</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>137500</v>
+      </c>
+      <c r="J21" s="3">
         <v>164900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>253400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>174400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>184600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>192400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>201100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>119100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>102800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>148100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>209500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>167400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>122400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>143600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>152800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>117100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>77400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>99200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>171700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>90300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>67800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>109700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>188800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>86400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>69000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>106300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>181000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>81000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
         <v>14500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>14500</v>
+      </c>
+      <c r="G22" s="3">
         <v>16700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>16200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>14900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>15000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>14700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>14100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>11500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>9200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>8000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>7000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>7000</v>
       </c>
       <c r="P22" s="3">
         <v>7000</v>
       </c>
       <c r="Q22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="R22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="S22" s="3">
         <v>7100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>7500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>8000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>8300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>8700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>8200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>8400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>9000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>6700</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>4700</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>4900</v>
       </c>
       <c r="AB22" s="3">
         <v>4700</v>
       </c>
       <c r="AC22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD22" s="3">
         <v>4700</v>
       </c>
-      <c r="AD22" s="3">
-        <v>4800</v>
-      </c>
       <c r="AE22" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="AF22" s="3">
         <v>4800</v>
       </c>
       <c r="AG22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AI22" s="3">
         <v>4700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>4900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>109300</v>
+      </c>
+      <c r="F23" s="3">
         <v>144200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>179200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>80100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>86900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-28600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>210800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>131300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>143300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>157100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>165100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>87100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>69300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>117500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>177200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>135800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>88600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>111000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>121400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>86100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>43700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>71200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>137200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>70000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>43600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>93300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>169200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>66400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>46900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>88400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>158300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>59600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F24" s="3">
         <v>24900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>34400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>15200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>16600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-13600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>43300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>24400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>25700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>31900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>33900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>17600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>9200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>21100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>35100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>24500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>16400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>22000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>22900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>16000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>5500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>11600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>21600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>10500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>4400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>14800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>37900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>10700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>13100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>20000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>37800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>14600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2428,210 +2526,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>89900</v>
+      </c>
+      <c r="F26" s="3">
         <v>119300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>144800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>64900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>70300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-15000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>167500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>106900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>117600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>125200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>131100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>69500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>60100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>96300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>142200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>111300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>72200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>89000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>98400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>70100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>38200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>59700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>115600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>59500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>39100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>78500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>131300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>55700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>33800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>68400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>120500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>45000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>89900</v>
+      </c>
+      <c r="F27" s="3">
         <v>119300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>144800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>64900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>70300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-15000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>167500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>106900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>117600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>125200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>131100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>69500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>60100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>96300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>142200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>111300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>72200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>89000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>98400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>70100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>38200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>59700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>115600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>59500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>39100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>78500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>131300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>55700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>33800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>68400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>120500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>45000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2731,8 +2847,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2775,11 +2897,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2793,35 +2915,35 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>900</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>500</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-33100</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2832,8 +2954,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2933,8 +3061,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3034,210 +3168,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F32" s="3">
         <v>10600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>8300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>7700</v>
       </c>
-      <c r="G32" s="3">
-        <v>7100</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J32" s="3">
         <v>5500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>6700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>9000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-3100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-3300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-3100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-8800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>89900</v>
+      </c>
+      <c r="F33" s="3">
         <v>119300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>144800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>64900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>70300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-15000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>167500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>106900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>117600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>125200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>131100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>69500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>60100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>96300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>142200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>111300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>72200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>89000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>98400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>70100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>38300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>60600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>115600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>59500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>39000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>79000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>131300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>22600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>33800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>68400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>120500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>45000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3337,215 +3489,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>89900</v>
+      </c>
+      <c r="F35" s="3">
         <v>119300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>144800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>64900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>70300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-15000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>167500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>106900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>117600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>125200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>131100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>69500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>60100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>96300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>142200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>111300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>72200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>89000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>98400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>70100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>38300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>60600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>115600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>59500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>39000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>79000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>131300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>22600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>33800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>68400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>120500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>45000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45506</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45415</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45324</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45142</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45051</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44960</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44771</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44680</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44589</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44407</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44225</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43952</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43679</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43588</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43497</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43315</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43224</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43133</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42951</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42860</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42769</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3581,8 +3751,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3618,109 +3790,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>199500</v>
+      </c>
+      <c r="F41" s="3">
         <v>221100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>188800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>198500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>193100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>147900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>151300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>174000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>188300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>231600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>263200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>193000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>405600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>535300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>497600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>433400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>479900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>394100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>200000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>108900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>151800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>143300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>180100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>250000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>289100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>250900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>206100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>219700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>310300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>335000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>265200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>158900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>273600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3820,477 +4000,507 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>494300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>459700</v>
+      </c>
+      <c r="F43" s="3">
         <v>532300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>623100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>489100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>407400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>390700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>462000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>377300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>332700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>350700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>439300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>366300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>310300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>301200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>391200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>306900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>261100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>294700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>400400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>321200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>268800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>312200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>428600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>225500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>193200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>219500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>329600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>198700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>183100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>221600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>328500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>183900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>326500</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1143100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1038900</v>
+      </c>
+      <c r="F44" s="3">
         <v>1082000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1105000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1177100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1087800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1112700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1127500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1131400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1051100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>939300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>891700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>832100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>738200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>665600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>628800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>675300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>652400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>656200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>714200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>739000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>651700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>620600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>611300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>416700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>358300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>364500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>394800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>439300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>329000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>349000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>341600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>402100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>12000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>9800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>16800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>13800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>15000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>10600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>103300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>82900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>69400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>46000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>35100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>43600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>41800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>41200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>34200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>39200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>59900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>51400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>50600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>54200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>50300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>41800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>54100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>38200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>47800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>43000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>37600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>42600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>41300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>36500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1896200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1764900</v>
+      </c>
+      <c r="F46" s="3">
         <v>1913900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2019200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1966500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1798800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1731800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1826800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1757700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1675400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1604400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1663700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1437300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1489200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1545800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1559500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1456700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1427600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1384200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1374600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1220500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1122900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1130400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1270300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>933900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>894600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>873000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>978200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>900800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>859900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>948100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>976600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>781300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F47" s="3">
         <v>46400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>51700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>48400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>50600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>48500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>53200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>45700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>39300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>31400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>30900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>24100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>20700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>19300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>25300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>23000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>19700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>22600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>27800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>25300</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>8</v>
@@ -4304,11 +4514,11 @@
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
@@ -4325,210 +4535,228 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>750800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>759300</v>
+      </c>
+      <c r="F48" s="3">
         <v>748900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>755100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>761000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>767000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>741600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>677600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>658700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>647800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>605200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>588000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>585900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>554700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>529200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>527300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>532600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>546700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>539500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>537900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>504400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>437300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>426400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>425400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>279300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>271500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>249500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>245300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>234400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>235200</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>226900</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>224300</v>
       </c>
       <c r="AH48" s="3">
         <v>226900</v>
       </c>
       <c r="AI48" s="3">
+        <v>224300</v>
+      </c>
+      <c r="AJ48" s="3">
+        <v>226900</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1060100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>940400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>949000</v>
+      </c>
+      <c r="F49" s="3">
         <v>962600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>973400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>982700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>990900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1000500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1153000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1161600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1169100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1178900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1170900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1177700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>841700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>848500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>855200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>832800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>832400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>837500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>844100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>709800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>714600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>700400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>705500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>331100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>330900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>333100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>335400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>308300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>308800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>308900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>310200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>312000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>302900</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4628,8 +4856,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4729,109 +4963,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F52" s="3">
         <v>21300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>21800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>22200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>22800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>21800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>19400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>19400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>24400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>20100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>25900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>28100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>29800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>25300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>28800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>30100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>26800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>30000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>27200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>31600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>55700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>52500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>64800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>78500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>73900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>79200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>76700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>73200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>89900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>85500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>87700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>82700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>80700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4931,109 +5177,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3696700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3582800</v>
+      </c>
+      <c r="F54" s="3">
         <v>3731400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3852200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3801100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3644300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3585900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3741400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3654900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3556000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3439900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3479300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3253000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2936100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2968000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2996100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2875100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2853200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2813900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2811500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2491600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2330500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2309700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2466000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1622800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1571000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1534800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1635700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1516800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1493800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1569500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1598800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1402900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1384600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5069,8 +5327,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5106,614 +5366,652 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>447100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>452700</v>
+      </c>
+      <c r="F57" s="3">
         <v>437800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>512400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>421800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>430000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>407400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>514800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>475200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>578600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>487000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>566800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>474500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>503100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>411400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>421700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>364400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>364000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>268700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>327400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>348000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>319200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>304700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>391700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>281500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>256600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>229000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>303900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>266600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>211800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>211500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>273600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>232400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>30300</v>
+      </c>
+      <c r="F58" s="3">
         <v>45000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>33100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>25600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>19500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>17800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>15900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>16000</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>65000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>100000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>100000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>104200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>100000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>10000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>99900</v>
-      </c>
-      <c r="T58" s="3">
-        <v>108900</v>
       </c>
       <c r="U58" s="3">
         <v>99900</v>
       </c>
       <c r="V58" s="3">
+        <v>108900</v>
+      </c>
+      <c r="W58" s="3">
+        <v>99900</v>
+      </c>
+      <c r="X58" s="3">
         <v>113900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>79900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>99900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>90000</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
         <v>13000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>13000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>26300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>23100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>23900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>23000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>153700</v>
+      </c>
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
-        <v>148600</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>143900</v>
+      </c>
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>154100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>485000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>459200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>444000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>411600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>433900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>442800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>467200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>445200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>392000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>419500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>428500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>362400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>357800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>351900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>360100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>283500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>276100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>282600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>335500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>292900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>283800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>309400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>324900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>263700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>479800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>993100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>976000</v>
+      </c>
+      <c r="F60" s="3">
         <v>984400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1048700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>921900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>948600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>907500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1024000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>988000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1063600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1011300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1110700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>986100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>937000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>958400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>988900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>819500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>855800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>797100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>855700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>824300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>757000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>756400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>841800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>565000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>532600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>511700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>652400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>572500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>521800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>543900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>622400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>519100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>463800</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1190200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1010900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1065700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1106500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1288200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1143600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1162500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1099100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1151700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>990800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>990600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>991000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>991400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>691200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>587300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>591500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>691400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>691300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>782000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>790900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>601000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>620900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>620800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>721100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>312600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>312500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>312500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>299300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>302500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>305600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>308800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>312000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>315300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>328500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>43500</v>
+      </c>
+      <c r="F62" s="3">
         <v>44500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>45200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>42700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>40800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>38700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>39700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>39700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>149900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>151500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>154100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>156100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>156700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>185100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>186300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>184500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>191400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>180700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>179900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>154200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>93100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>88700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>97900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>50900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>56900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>60400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>60700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>61100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>49300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>56900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>56600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>55400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5813,8 +6111,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5914,8 +6218,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6015,109 +6325,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2229100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2030900</v>
+      </c>
+      <c r="F66" s="3">
         <v>2095000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2200800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2253200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2133400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2108800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2181400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2210800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2204300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2153300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2255800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2133500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1785000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1730900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1766700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1695400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1738400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1759800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1826500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1579600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1471000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1465900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1660700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>928400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>902100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>884500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1012400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>936000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>876700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>909600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>991000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>889900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>834500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6153,8 +6475,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6254,8 +6578,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6355,8 +6685,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6456,8 +6792,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6557,109 +6899,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1414500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1496400</v>
+      </c>
+      <c r="F72" s="3">
         <v>1576200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1583200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1478900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1444100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1403800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1485000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1368500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1280900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1213600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1146800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1040600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1071900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1157400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1151800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1104300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1041500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>981300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>911500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>837200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>784900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>763900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>724000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>613200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>587300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>568400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>538500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>490400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>534300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>578600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>535600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>443600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>480000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6759,8 +7113,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6860,8 +7220,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6961,109 +7327,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1467600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1551900</v>
+      </c>
+      <c r="F76" s="3">
         <v>1636400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1651400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1547900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1510900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1477100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1560000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1444200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1351700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1286600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1223500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1119500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1151100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1237200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1229400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1179700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1114800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1054000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>985000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>912100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>859600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>843800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>805300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>694400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>668900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>650200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>623300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>580800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>617100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>659900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>607800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>513000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7163,215 +7541,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45506</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45415</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45324</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45142</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45051</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44960</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44771</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44680</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44589</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44407</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44225</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43952</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43679</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43588</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43497</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43315</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43224</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43133</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42951</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42860</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42769</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>89900</v>
+      </c>
+      <c r="F81" s="3">
         <v>119300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>144800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>64900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>70300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-15000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>167500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>106900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>117600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>125200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>131100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>69500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>60100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>96300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>142200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>111300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>72200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>89000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>98400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>70100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>38300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>60600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>115600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>59500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>39000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>79000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>131300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>22600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>33800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>68400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>120500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>45000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7407,109 +7803,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F83" s="3">
         <v>18300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>19100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>19200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>20600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>17000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>18800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>18500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>29800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>26100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>28000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>24900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>26500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>23600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>25100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>24100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>25800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>24300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>22800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>22800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>25300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>19000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>27900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>15600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>19400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>11800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>14900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>15200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>17300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>13200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>18000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>16500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7609,8 +8013,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7710,8 +8120,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7811,8 +8227,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7912,8 +8334,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8013,109 +8441,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>240100</v>
+      </c>
+      <c r="F89" s="3">
         <v>194700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>227300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-92200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>152100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>93000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>130600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-68900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>142600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>111700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>132900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-90000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>78300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>158500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>223600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>95000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>233500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>235000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>94200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-23300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>78300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>95100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>138000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>26000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>105400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>120900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>130300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>8100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>84100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>106200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>155000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>15400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>80300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8151,109 +8591,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-39900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-24900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-20400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-19100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-43800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-35600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-40800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-29300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-67700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-47000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-24100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-11900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-56100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-15700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-10500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-31400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-19500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-15300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-11800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-36100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-23400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-21700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-32900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-32200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8353,8 +8801,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8454,109 +8908,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-18400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-38500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-56500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-40800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-21900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-67700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-41700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-25600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-413400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-57800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-47400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-2100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-31400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-21100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-151800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-11800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-28800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-18600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-698700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-26800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8592,109 +9058,117 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>36900</v>
+      </c>
+      <c r="F96" s="3">
         <v>37500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>37500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>37600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>35400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>35400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>35600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>35500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-31300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-31400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-31500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-31500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-27800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-28200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-28400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-27000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-26900</v>
       </c>
       <c r="V96" s="3">
         <v>-26900</v>
       </c>
       <c r="W96" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="X96" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-24100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-24100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-23900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-21200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-21100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-21300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-21400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-18800</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-18900</v>
       </c>
       <c r="AH96" s="3">
         <v>-19000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8794,8 +9268,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8895,8 +9375,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8996,307 +9482,331 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-244600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-157100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-217500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>114100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-65100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-50200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-106600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>74400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-120500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-99700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-30900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>293300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-152500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-97100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-111100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-143000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-116800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-24000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>150600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-7500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-40300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-113700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>491800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-38300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-23300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-51900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-88700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-88100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-82900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-32600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-33500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-96300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-64700</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F101" s="3">
         <v>10300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-5900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-6200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-6200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="O101" s="3">
-        <v>2200</v>
       </c>
       <c r="P101" s="3">
         <v>-2500</v>
       </c>
       <c r="Q101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>3600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>4200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>7800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>1800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="F102" s="3">
         <v>32300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-9700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>45200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-22700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-14200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-43300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-31700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>70300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-212700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-129700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>37700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>64200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-46500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>85800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>194100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>91100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-42900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>8500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-36800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-69900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-39200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>38300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>44800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-13600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-90500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>69800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>106300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-114700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-3700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>TTC</t>
   </si>
@@ -656,486 +656,499 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45779</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45506</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45415</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45324</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45142</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45051</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44960</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44771</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44680</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44589</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44407</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44225</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43952</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43679</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43588</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43497</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43315</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43224</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43133</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42951</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42860</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42769</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1317900</v>
+      </c>
+      <c r="E8" s="3">
         <v>995000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1076000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1156900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1349000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1001900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>983200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1081800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1339300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1148800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1172000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1160600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1249500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>932700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>960700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>976800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1149100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>873000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>841000</v>
       </c>
       <c r="V8" s="3">
         <v>841000</v>
       </c>
       <c r="W8" s="3">
+        <v>841000</v>
+      </c>
+      <c r="X8" s="3">
         <v>929400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>767500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>734400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>838700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>962000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>603000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>539300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>655800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>875300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>548200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>488600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>627900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>872800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>515800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>468400</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>877500</v>
+      </c>
+      <c r="E9" s="3">
         <v>655600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>733900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>747200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>896000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>657400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>653600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>709400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>859600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>752700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>773100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>760600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>844100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>632200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>671300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>645700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>746200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>558000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>540600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>546400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>622700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>479400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>489300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>572700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>640700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>387300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>360200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>422200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>551200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>344000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>304400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>401200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>556500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>322400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>440400</v>
+      </c>
+      <c r="E10" s="3">
         <v>339400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>342100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>409700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>453000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>344500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>329600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>372400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>479700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>396100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>398900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>400000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>405400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>300500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>289400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>331100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>402900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>315100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>300400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>294600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>306700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>288100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>245100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>266000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>321300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>215700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>179100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>233600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>324100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>204200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>184200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>226700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>316300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>193400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>172200</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1173,19 +1186,20 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>173100</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1193,11 +1207,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>173900</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1280,8 +1294,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1387,40 +1404,43 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>20000</v>
+        <v>5600</v>
       </c>
       <c r="E14" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F14" s="3">
         <v>-19200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>151300</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>700</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1428,29 +1448,29 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>5800</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-17100</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1494,41 +1514,44 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E15" s="3">
         <v>32100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>30900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>30700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>27200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>27900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>28300</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1601,8 +1624,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1637,222 +1663,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>897200</v>
+        <v>1137500</v>
       </c>
       <c r="E17" s="3">
+        <v>901000</v>
+      </c>
+      <c r="F17" s="3">
         <v>985800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>997900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1157000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>909400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>888500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>949600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1120500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1011700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1021600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>997500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1078900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>841000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>886500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>854900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>968400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>731500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>747500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>725000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>803600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>676400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>691100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>764800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>824300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>532900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>496300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>562900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>705000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>481300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>441200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>540200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>713500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>455300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>424800</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>97800</v>
+        <v>180400</v>
       </c>
       <c r="E18" s="3">
+        <v>94000</v>
+      </c>
+      <c r="F18" s="3">
         <v>90200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>159000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>192000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>92500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>94700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>132200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>218800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>137100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>150400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>163100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>170600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>91700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>74200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>121900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>180700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>141500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>93500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>116000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>125800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>91100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>43300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>73900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>137700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>70100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>43000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>92900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>170300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>66900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>47400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>87700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>159300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>60500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1890,263 +1923,270 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-14400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>2500</v>
       </c>
       <c r="P20" s="3">
         <v>2500</v>
       </c>
       <c r="Q20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R20" s="3">
         <v>2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>6300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3600</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>4300</v>
       </c>
       <c r="AG20" s="3">
         <v>4300</v>
       </c>
       <c r="AH20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AI20" s="3">
         <v>5400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>133200</v>
+        <v>221600</v>
       </c>
       <c r="E21" s="3">
+        <v>129400</v>
+      </c>
+      <c r="F21" s="3">
         <v>141000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>230500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>130900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>137500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>164900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>253400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>174400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>184600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>192400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>201100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>119100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>102800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>148100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>209500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>167400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>122400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>143600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>152800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>117100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>77400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>99200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>171700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>90300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>67800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>109700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>188800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>86400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>69000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>106300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>181000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>81000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E22" s="3">
         <v>15000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>14500</v>
       </c>
       <c r="F22" s="3">
         <v>14500</v>
       </c>
       <c r="G22" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H22" s="3">
         <v>16700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>7000</v>
       </c>
       <c r="Q22" s="3">
         <v>7000</v>
@@ -2155,46 +2195,46 @@
         <v>7000</v>
       </c>
       <c r="S22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="T22" s="3">
         <v>7100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4900</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>4700</v>
       </c>
       <c r="AE22" s="3">
         <v>4700</v>
       </c>
       <c r="AF22" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="AG22" s="3">
         <v>4800</v>
@@ -2203,230 +2243,239 @@
         <v>4800</v>
       </c>
       <c r="AI22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>4900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>168700</v>
+      </c>
+      <c r="E23" s="3">
         <v>66100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>109300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>144200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>179200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>80100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>86900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>210800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>131300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>143300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>157100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>165100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>87100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>69300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>117500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>177200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>135800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>88600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>111000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>121400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>86100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>43700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>71200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>137200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>70000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>43600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>93300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>169200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>66400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>46900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>88400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>158300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>59600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E24" s="3">
         <v>13300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>24900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>34400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-13600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>43300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>25700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>33900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>17600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>35100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>22000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>22900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>11600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>14800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>37900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>20000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>37800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>14600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2532,222 +2581,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E26" s="3">
         <v>52800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>89900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>119300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>144800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>64900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>70300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>167500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>106900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>117600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>125200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>131100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>69500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>60100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>96300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>142200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>111300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>72200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>89000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>98400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>70100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>38200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>59700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>115600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>59500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>39100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>78500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>131300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>55700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>33800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>68400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>120500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>45000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E27" s="3">
         <v>52800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>89900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>119300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>144800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>64900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>70300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>167500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>106900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>117600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>125200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>131100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>69500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>60100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>96300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>142200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>111300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>72200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>89000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>98400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>70100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>38200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>59700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>115600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>59500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>39100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>78500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>131300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>55700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>33800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>68400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>120500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>45000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2853,8 +2911,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2903,8 +2964,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2921,32 +2982,32 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>900</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>500</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-33100</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2960,8 +3021,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3067,8 +3131,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3174,222 +3241,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E32" s="3">
         <v>3300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>14400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-2500</v>
       </c>
       <c r="P32" s="3">
         <v>-2500</v>
       </c>
       <c r="Q32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="R32" s="3">
         <v>-2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-4300</v>
       </c>
       <c r="AG32" s="3">
         <v>-4300</v>
       </c>
       <c r="AH32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E33" s="3">
         <v>52800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>89900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>119300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>144800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>64900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>70300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>167500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>106900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>117600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>125200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>131100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>69500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>60100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>96300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>142200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>111300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>72200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>89000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>98400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>70100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>38300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>60600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>115600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>59500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>39000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>79000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>131300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>22600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>33800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>68400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>120500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>45000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3495,227 +3571,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E35" s="3">
         <v>52800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>89900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>119300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>144800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>64900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>70300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>167500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>106900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>117600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>125200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>131100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>69500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>60100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>96300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>142200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>111300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>72200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>89000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>98400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>70100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>38300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>60600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>115600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>59500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>39000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>79000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>131300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>22600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>33800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>68400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>120500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>45000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45779</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45506</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45415</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45324</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45142</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45051</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44960</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44771</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44680</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44589</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44407</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44225</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43952</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43679</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43588</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43497</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43315</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43224</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43133</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42951</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42860</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42769</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3753,8 +3838,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3792,115 +3878,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>176500</v>
+      </c>
+      <c r="E41" s="3">
         <v>171300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>199500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>221100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>188800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>198500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>193100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>147900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>151300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>174000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>188300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>231600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>263200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>193000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>405600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>535300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>497600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>433400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>479900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>394100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>200000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>108900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>151800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>143300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>180100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>250000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>289100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>250900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>206100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>219700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>310300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>335000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>265200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>158900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>273600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4006,504 +4096,519 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>602500</v>
+      </c>
+      <c r="E43" s="3">
         <v>494300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>459700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>532300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>623100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>489100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>407400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>390700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>462000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>377300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>332700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>350700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>439300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>366300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>310300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>301200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>391200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>306900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>261100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>294700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>400400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>321200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>268800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>312200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>428600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>225500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>193200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>219500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>329600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>198700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>183100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>221600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>328500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>183900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>326500</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1119800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1143100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1038900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1082000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1105000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1177100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1087800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1112700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1127500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1131400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1051100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>939300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>891700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>832100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>738200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>665600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>628800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>675300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>652400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>656200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>714200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>739000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>651700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>620600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>611300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>416700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>358300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>364500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>394800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>439300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>329000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>349000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>341600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>402100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>13600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>103300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>82900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>69400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>46000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>43600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>41800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>41200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>34200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>59900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>51400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>50600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>54200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>50300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>41800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>54100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>38200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>47800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>43000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>37600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>42600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>41300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>36500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1978900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1896200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1764900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1913900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2019200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1966500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1798800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1731800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1826800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1757700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1675400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1604400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1663700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1437300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1489200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1545800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1559500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1456700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1427600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1384200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1374600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1220500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1122900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1130400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1270300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>933900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>894600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>873000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>978200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>900800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>859900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>948100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>976600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>781300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E47" s="3">
         <v>48000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>49200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>46400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>51700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>48400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>50600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>48500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>53200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>39300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>30900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>24100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>20700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>19300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>25300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>23000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>19700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>22600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>27800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>25300</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
@@ -4520,8 +4625,8 @@
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
@@ -4541,222 +4646,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>746700</v>
+      </c>
+      <c r="E48" s="3">
         <v>750800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>759300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>748900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>755100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>761000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>767000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>741600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>677600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>658700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>647800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>605200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>588000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>585900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>554700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>529200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>527300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>532600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>546700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>539500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>537900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>504400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>437300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>426400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>425400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>279300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>271500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>249500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>245300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>234400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>235200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>226900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>224300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>226900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1060100</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>938100</v>
+      </c>
+      <c r="E49" s="3">
         <v>940400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>949000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>962600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>973400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>982700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>990900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1000500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1153000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1161600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1169100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1178900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1170900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1177700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>841700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>848500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>855200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>832800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>832400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>837500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>844100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>709800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>714600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>700400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>705500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>331100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>330900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>333100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>335400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>308300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>308800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>308900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>310200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>312000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>302900</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4862,8 +4976,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4969,115 +5086,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E52" s="3">
         <v>15100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21800</v>
-      </c>
-      <c r="K52" s="3">
-        <v>19400</v>
       </c>
       <c r="L52" s="3">
         <v>19400</v>
       </c>
       <c r="M52" s="3">
+        <v>19400</v>
+      </c>
+      <c r="N52" s="3">
         <v>24400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>25300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>30000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>27200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>31600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>55700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>52500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>64800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>78500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>73900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>79200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>76700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>73200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>89900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>85500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>87700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>82700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>80700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5183,115 +5306,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3788100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3696700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3582800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3731400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3852200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3801100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3644300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3585900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3741400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3654900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3556000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3439900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3479300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3253000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2936100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2968000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2996100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2875100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2853200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2813900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2811500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2491600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2330500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2309700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2466000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1622800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1571000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1534800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1635700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1516800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1493800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1569500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1598800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1402900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1384600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5329,8 +5458,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5368,193 +5498,197 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>516000</v>
+      </c>
+      <c r="E57" s="3">
         <v>447100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>452700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>437800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>512400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>421800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>430000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>407400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>514800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>475200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>578600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>487000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>566800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>474500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>503100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>411400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>421700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>364400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>364000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>268700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>327400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>348000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>319200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>304700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>391700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>281500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>256600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>229000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>303900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>266600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>211800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>211500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>273600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>232400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E58" s="3">
         <v>34700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>30300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>33100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>25600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16000</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>65000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>100000</v>
       </c>
       <c r="P58" s="3">
         <v>100000</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>104200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>100000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>10000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>99900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>108900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>99900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>113900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>79900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>99900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>90000</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
       <c r="AC58" s="3">
         <v>0</v>
       </c>
@@ -5562,456 +5696,471 @@
         <v>0</v>
       </c>
       <c r="AE58" s="3">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>13000</v>
       </c>
       <c r="AG58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AH58" s="3">
         <v>26300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>23100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>23900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>23000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E59" s="3">
         <v>4800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>153700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>143900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>154100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>485000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>459200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>444000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>411600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>433900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>442800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>467200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>445200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>392000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>419500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>428500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>362400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>357800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>351900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>360100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>283500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>276100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>282600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>335500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>292900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>283800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>309400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>324900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>263700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>479800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1091200</v>
+      </c>
+      <c r="E60" s="3">
         <v>993100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>976000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>984400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1048700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>921900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>948600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>907500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1024000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>988000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1063600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1011300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1110700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>986100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>937000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>958400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>988900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>819500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>855800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>797100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>855700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>824300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>757000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>756400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>841800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>565000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>532600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>511700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>652400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>572500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>521800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>543900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>622400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>519100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>463800</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1173300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1190200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1010900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1065700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1106500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1288200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1143600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1162500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1099100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1151700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>990800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>990600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>991000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>991400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>691200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>587300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>591500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>691400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>691300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>782000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>790900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>601000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>620900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>620800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>721100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>312600</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>312500</v>
       </c>
       <c r="AD61" s="3">
         <v>312500</v>
       </c>
       <c r="AE61" s="3">
+        <v>312500</v>
+      </c>
+      <c r="AF61" s="3">
         <v>299300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>302500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>305600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>308800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>312000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>315300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>328500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E62" s="3">
         <v>45300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>43500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>44500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38700</v>
-      </c>
-      <c r="K62" s="3">
-        <v>39700</v>
       </c>
       <c r="L62" s="3">
         <v>39700</v>
       </c>
       <c r="M62" s="3">
+        <v>39700</v>
+      </c>
+      <c r="N62" s="3">
         <v>149900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>151500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>154100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>156100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>156700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>185100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>186300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>184500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>191400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>180700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>179900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>154200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>93100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>88700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>97900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>50900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>56900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>60400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>60700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>61100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>49300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>56900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>56600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>55400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6117,8 +6266,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6224,8 +6376,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6331,115 +6486,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2311500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2229100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2030900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2095000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2200800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2253200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2133400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2108800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2181400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2210800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2204300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2153300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2255800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2133500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1785000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1730900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1766700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1695400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1738400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1759800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1826500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1579600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1471000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1465900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1660700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>928400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>902100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>884500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1012400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>936000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>876700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>909600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>991000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>889900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>834500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6477,8 +6638,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6584,8 +6746,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6691,8 +6856,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6798,8 +6966,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6905,115 +7076,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1419600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1414500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1496400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1576200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1583200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1478900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1444100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1403800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1485000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1368500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1280900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1213600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1146800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1040600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1071900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1157400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1151800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1104300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1041500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>981300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>911500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>837200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>784900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>763900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>724000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>613200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>587300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>568400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>538500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>490400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>534300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>578600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>535600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>443600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>480000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7119,8 +7296,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7226,8 +7406,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7333,115 +7516,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1476600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1467600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1551900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1636400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1651400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1547900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1510900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1477100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1560000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1444200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1351700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1286600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1223500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1119500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1151100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1237200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1229400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1179700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1114800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1054000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>985000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>912100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>859600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>843800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>805300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>694400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>668900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>650200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>623300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>580800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>617100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>659900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>607800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>513000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7547,227 +7736,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45779</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45506</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45415</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45324</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45142</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45051</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44960</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44771</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44680</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44589</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44407</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44225</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43952</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43679</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43588</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43497</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43315</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43224</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43133</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42951</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42860</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42769</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E81" s="3">
         <v>52800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>89900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>119300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>144800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>64900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>70300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>167500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>106900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>117600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>125200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>131100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>69500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>60100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>96300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>142200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>111300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>72200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>89000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>98400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>70100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>38300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>60600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>115600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>59500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>39000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>79000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>131300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>22600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>33800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>68400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>120500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>45000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7805,115 +8003,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E83" s="3">
         <v>22000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>19200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>28000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>26500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>23600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>25100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>24300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>22800</v>
       </c>
       <c r="X83" s="3">
         <v>22800</v>
       </c>
       <c r="Y83" s="3">
+        <v>22800</v>
+      </c>
+      <c r="Z83" s="3">
         <v>25300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>19000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>27900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>11800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>14900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>15200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>17300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>13200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>16500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8019,8 +8221,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8126,8 +8331,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8233,8 +8441,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8340,8 +8551,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8447,115 +8661,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>171700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-48600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>240100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>194700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>227300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-92200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>152100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>93000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>130600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-68900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>142600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>111700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>132900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>78300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>158500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>223600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>95000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>233500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>235000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>94200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-23300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>78300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>95100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>138000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>26000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>105400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>120900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>130300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>84100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>106200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>155000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>15400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>80300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8593,115 +8813,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-39900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-43800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-35600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-29300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-67700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-47000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-56100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-31400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-23400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-21700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-32900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-32200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8807,8 +9031,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8914,115 +9141,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-56500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-67700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-413400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-57800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-21200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-47400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-31400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-21100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-151800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-28800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-698700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-10900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9060,67 +9293,68 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E96" s="3">
         <v>38500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>36900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>37500</v>
       </c>
       <c r="G96" s="3">
         <v>37500</v>
       </c>
       <c r="H96" s="3">
+        <v>37500</v>
+      </c>
+      <c r="I96" s="3">
         <v>37600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>35400</v>
       </c>
       <c r="J96" s="3">
         <v>35400</v>
       </c>
       <c r="K96" s="3">
+        <v>35400</v>
+      </c>
+      <c r="L96" s="3">
         <v>35600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>35500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-31300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-31400</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-31500</v>
       </c>
       <c r="P96" s="3">
         <v>-31500</v>
       </c>
       <c r="Q96" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="R96" s="3">
         <v>-27800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-28100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-28200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-28400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-27000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-26900</v>
       </c>
       <c r="W96" s="3">
         <v>-26900</v>
@@ -9129,46 +9363,49 @@
         <v>-26900</v>
       </c>
       <c r="Y96" s="3">
-        <v>-24100</v>
+        <v>-26900</v>
       </c>
       <c r="Z96" s="3">
         <v>-24100</v>
       </c>
       <c r="AA96" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-23900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-21200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-21100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-21300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-21400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-18900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9274,8 +9511,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9381,8 +9621,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9488,325 +9731,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-149500</v>
+      </c>
+      <c r="E100" s="3">
         <v>44600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-244600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-157100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-217500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>114100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-65100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-50200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-106600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>74400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-120500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-99700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-30900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>293300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-152500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-97100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-111100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-143000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-116800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-24000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>150600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-40300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-113700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>491800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-38300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-23300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-88700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-88100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-82900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-32600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-33500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-96300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-64700</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>7800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>45200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-43300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>70300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-212700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-129700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>37700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>64200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-46500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>85800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>194100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>91100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-42900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>8500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-36800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-69900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-39200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>38300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>44800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-13600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-90500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>69800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>106300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-114700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-3700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>TTC</t>
   </si>
@@ -656,512 +656,538 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45870</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45779</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45506</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45415</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45324</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45142</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45051</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44960</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44771</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44680</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44589</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44407</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44225</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43952</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43679</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43588</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43497</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43315</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43224</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43133</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42951</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42860</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42769</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1036300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1066200</v>
+      </c>
+      <c r="F8" s="3">
         <v>1131300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1317900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>995000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1076000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1156900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1349000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1001900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>983200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1081800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1339300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1148800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1172000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1160600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1249500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>932700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>960700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>976800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1149100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>873000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>841000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>841000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>929400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>767500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>734400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>838700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>962000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>603000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>539300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>655800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>875300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>548200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>488600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>627900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>872800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>515800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>468400</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>689700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>730200</v>
+      </c>
+      <c r="F9" s="3">
         <v>742300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>877500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>655600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>733900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>747200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>896000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>657400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>653600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>709400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>859600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>752700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>773100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>760600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>844100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>632200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>671300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>645700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>746200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>558000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>540600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>546400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>622700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>479400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>489300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>572700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>640700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>387300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>360200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>422200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>551200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>344000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>304400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>401200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>556500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>322400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>346600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>336000</v>
+      </c>
+      <c r="F10" s="3">
         <v>389000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>440400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>339400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>342100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>409700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>453000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>344500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>329600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>372400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>479700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>396100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>398900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>400000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>405400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>300500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>289400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>331100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>402900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>315100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>300400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>294600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>306700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>288100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>245100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>266000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>321300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>215700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>179100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>233600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>324100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>204200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>184200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>226700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>316300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>193400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>172200</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1201,40 +1227,42 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>162300</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
-        <v>173100</v>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>173100</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
-        <v>173900</v>
+      <c r="K12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
+      <c r="M12" s="3">
+        <v>173900</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1314,8 +1342,14 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1427,80 +1461,86 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="F14" s="3">
         <v>89200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>5600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>16200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-19200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>10900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>4400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>3900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>151300</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
-        <v>700</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>700</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>5800</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-17100</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
@@ -1540,50 +1580,56 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>47100</v>
+      </c>
+      <c r="F15" s="3">
         <v>32200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>31500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>32100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>36400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>30900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>30200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>30700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>35800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>27200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>27900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>28300</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1653,8 +1699,14 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1691,234 +1743,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>934600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1003300</v>
+      </c>
+      <c r="F17" s="3">
         <v>977300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1137500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>901000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>985800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>997900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1157000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>909400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>888500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>949600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1120500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1011700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1021600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>997500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1078900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>841000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>886500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>854900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>968400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>731500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>747500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>725000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>803600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>676400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>691100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>764800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>824300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>532900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>496300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>562900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>705000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>481300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>441200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>540200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>713500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>455300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>424800</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>101700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>62900</v>
+      </c>
+      <c r="F18" s="3">
         <v>154000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>180400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>94000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>90200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>159000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>192000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>92500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>94700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>132200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>218800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>137100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>150400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>163100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>170600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>91700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>74200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>121900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>180700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>141500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>93500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>116000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>125800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>91100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>43300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>73900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>137700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>70100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>43000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>92900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>170300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>66900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>87700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>159300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>60500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,573 +2024,605 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-8100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-9700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-14400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-10600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-8300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-7700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-6700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>4300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>2600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>3100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>4200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>3100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>8800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>6300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>6200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>4700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>5500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>5100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>3600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>4300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>5400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>3700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>3900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>148900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>115400</v>
+      </c>
+      <c r="F21" s="3">
         <v>194300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>221600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>129400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>141000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>200500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>230500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>130900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>137500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>164900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>253400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>174400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>184600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>192400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>201100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>119100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>102800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>148100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>209500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>167400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>122400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>143600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>152800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>117100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>77400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>99200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>171700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>90300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>67800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>109700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>188800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>86400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>69000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>106300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>181000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>81000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F22" s="3">
         <v>15100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>15800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>15000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>14500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>14500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>16700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>16200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>14900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>15000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>14700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>14100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>11500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>9200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>8000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>7000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>7000</v>
       </c>
       <c r="T22" s="3">
         <v>7000</v>
       </c>
       <c r="U22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="V22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="W22" s="3">
         <v>7100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>7500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>8000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>8300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>8700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>8200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>8400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>9000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>6700</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>4700</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>4900</v>
       </c>
       <c r="AF22" s="3">
         <v>4700</v>
       </c>
       <c r="AG22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AH22" s="3">
         <v>4700</v>
       </c>
-      <c r="AH22" s="3">
-        <v>4800</v>
-      </c>
       <c r="AI22" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="AJ22" s="3">
         <v>4800</v>
       </c>
       <c r="AK22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AM22" s="3">
         <v>4700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>4900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>85000</v>
+      </c>
+      <c r="F23" s="3">
         <v>57800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>168700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>66100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>109300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>144200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>179200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>80100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>86900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-28600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>210800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>131300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>143300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>157100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>165100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>87100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>69300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>117500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>177200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>135800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>88600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>111000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>121400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>86100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>43700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>71200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>137200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>70000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>43600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>93300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>169200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>66400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>46900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>88400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>158300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>59600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F24" s="3">
         <v>4300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>31900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>13300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>19400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>24900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>34400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>15200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>16600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-13600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>43300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>24400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>25700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>31900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>33900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>17600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>9200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>21100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>35100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>24500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>16400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>22000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>22900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>16000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>5500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>11600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>21600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>10500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>4400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>14800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>37900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>10700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>13100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>20000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>37800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>14600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2636,234 +2734,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>73000</v>
+      </c>
+      <c r="F26" s="3">
         <v>53500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>136800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>52800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>89900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>119300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>144800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>64900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>70300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-15000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>167500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>106900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>117600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>125200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>131100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>69500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>60100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>96300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>142200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>111300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>72200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>89000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>98400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>70100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>38200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>59700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>115600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>59500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>39100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>78500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>131300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>55700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>68400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>120500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>45000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>73000</v>
+      </c>
+      <c r="F27" s="3">
         <v>53500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>136800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>52800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>89900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>119300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>144800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>64900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>70300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-15000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>167500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>106900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>117600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>125200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>131100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>69500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>60100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>96300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>142200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>111300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>72200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>89000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>98400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>70100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>38200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>59700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>115600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>59500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>39100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>78500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>131300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>55700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>68400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>120500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>45000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2975,8 +3091,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3031,11 +3153,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -3049,35 +3171,35 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>900</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>500</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-33100</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3088,8 +3210,14 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3201,8 +3329,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3314,234 +3448,252 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F32" s="3">
         <v>8100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>9700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>14400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>10600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>8300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>7700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>6700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-4300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-2600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-3100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>73000</v>
+      </c>
+      <c r="F33" s="3">
         <v>53500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>136800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>52800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>89900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>119300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>144800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>64900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>70300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-15000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>167500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>106900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>117600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>125200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>131100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>69500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>60100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>96300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>142200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>111300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>72200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>89000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>98400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>70100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>38300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>60600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>115600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>59500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>39000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>79000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>131300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>22600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>68400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>120500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>45000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3653,239 +3805,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>73000</v>
+      </c>
+      <c r="F35" s="3">
         <v>53500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>136800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>52800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>89900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>119300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>144800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>64900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>70300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-15000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>167500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>106900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>117600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>125200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>131100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>69500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>60100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>96300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>142200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>111300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>72200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>89000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>98400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>70100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>38300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>60600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>115600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>59500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>39000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>79000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>131300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>22600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>68400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>120500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>45000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45870</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45779</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45506</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45415</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45324</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45142</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45051</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44960</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44771</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44680</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44589</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44407</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44225</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43952</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43679</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43588</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43497</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43315</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43224</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43133</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42951</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42860</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42769</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3925,8 +4095,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3966,121 +4138,129 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>341000</v>
+      </c>
+      <c r="F41" s="3">
         <v>201000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>176500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>171300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>199500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>221100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>188800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>198500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>193100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>147900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>151300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>174000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>188300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>231600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>263200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>193000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>405600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>535300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>497600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>433400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>479900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>394100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>200000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>108900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>151800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>143300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>180100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>250000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>289100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>250900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>206100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>219700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>310300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>335000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>265200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>158900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>273600</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4192,537 +4372,567 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>486100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>378200</v>
+      </c>
+      <c r="F43" s="3">
         <v>472700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>602500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>494300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>459700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>532300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>623100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>489100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>407400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>390700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>462000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>377300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>332700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>350700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>439300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>366300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>310300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>301200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>391200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>306900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>261100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>294700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>400400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>321200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>268800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>312200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>428600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>225500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>193200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>219500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>329600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>198700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>183100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>221600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>328500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>183900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>326500</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>983700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>920800</v>
+      </c>
+      <c r="F44" s="3">
         <v>1036200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1119800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1143100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1038900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1082000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1105000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1177100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1087800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1112700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1127500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1131400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1051100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>939300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>891700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>832100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>738200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>665600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>628800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>675300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>652400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>656200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>714200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>739000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>651700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>620600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>611300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>416700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>358300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>364500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>394800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>439300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>329000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>349000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>341600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>402100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>13600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>12000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>9800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>16800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>13800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>15000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>10600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>103300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>82900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>69400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>46000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>35100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>43600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>41800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>41200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>34200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>39200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>59900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>51400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>50600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>54200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>50300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>41800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>54100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>38200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>47800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>43000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>37600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>42600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>41300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>36500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1736500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1705100</v>
+      </c>
+      <c r="F46" s="3">
         <v>1794100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1978900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1896200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1764900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1913900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2019200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1966500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1798800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1731800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1826800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1757700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1675400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1604400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1663700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1437300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1489200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1545800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1559500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1456700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1427600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1384200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1374600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1220500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1122900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1130400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1270300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>933900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>894600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>873000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>978200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>900800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>859900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>948100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>976600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>781300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F47" s="3">
         <v>41300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>51200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>48000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>49200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>46400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>51700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>48400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>50600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>48500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>53200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>45700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>39300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>31400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>30900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>24100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>20700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>19300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>25300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>23000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>19700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>22600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>27800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>25300</v>
-      </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
@@ -4736,11 +4946,11 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>0</v>
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
@@ -4757,234 +4967,252 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>730500</v>
+      </c>
+      <c r="F48" s="3">
         <v>734700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>746700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>750800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>759300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>748900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>755100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>761000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>767000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>741600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>677600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>658700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>647800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>605200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>588000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>585900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>554700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>529200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>527300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>532600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>546700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>539500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>537900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>504400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>437300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>426400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>425400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>279300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>271500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>249500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>245300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>234400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>235200</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>226900</v>
-      </c>
-      <c r="AK48" s="3">
-        <v>224300</v>
       </c>
       <c r="AL48" s="3">
         <v>226900</v>
       </c>
       <c r="AM48" s="3">
+        <v>224300</v>
+      </c>
+      <c r="AN48" s="3">
+        <v>226900</v>
+      </c>
+      <c r="AO48" s="3">
         <v>1060100</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1037800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>841200</v>
+      </c>
+      <c r="F49" s="3">
         <v>849400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>938100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>940400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>949000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>962600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>973400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>982700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>990900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1000500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1153000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1161600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1169100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1178900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1170900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1177700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>841700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>848500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>855200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>832800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>832400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>837500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>844100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>709800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>714600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>700400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>705500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>331100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>330900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>333100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>335400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>308300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>308800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>308900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>310200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>312000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>302900</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5096,8 +5324,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5209,121 +5443,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F52" s="3">
         <v>14700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>14600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>15100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>15400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>21300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>21800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>22200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>22800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>21800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>19400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>19400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>24400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>20100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>25900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>28100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>29800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>25300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>28800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>30100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>26800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>30000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>27200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>31600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>55700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>52500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>64800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>78500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>73900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>79200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>76700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>73200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>89900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>85500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>87700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>82700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>80700</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5435,121 +5681,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3702500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3438800</v>
+      </c>
+      <c r="F54" s="3">
         <v>3519800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3788100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3696700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3582800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3731400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3852200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3801100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3644300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3585900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3741400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3654900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3556000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3439900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3479300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3253000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2936100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2968000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2996100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2875100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2853200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2813900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2811500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2491600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2330500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2309700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2466000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1622800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1571000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1534800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1635700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1516800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1493800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1569500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1598800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>1402900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>1384600</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5589,8 +5847,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5630,686 +5890,724 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>437000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>367600</v>
+      </c>
+      <c r="F57" s="3">
         <v>385000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>516000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>447100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>452700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>437800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>512400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>421800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>430000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>407400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>514800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>475200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>578600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>487000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>566800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>474500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>503100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>411400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>421700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>364400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>364000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>268700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>327400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>348000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>319200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>304700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>391700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>281500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>256600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>229000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>303900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>266600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>211800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>211500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>273600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>232400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>19300</v>
+      </c>
+      <c r="F58" s="3">
         <v>36600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>38500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>34700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>30300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>45000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>33100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>25600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>19500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>17800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>15900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>16000</v>
       </c>
-      <c r="O58" s="3" t="s">
+      <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>65000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>100000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>100000</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>104200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>100000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>10000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>99900</v>
-      </c>
-      <c r="X58" s="3">
-        <v>108900</v>
       </c>
       <c r="Y58" s="3">
         <v>99900</v>
       </c>
       <c r="Z58" s="3">
+        <v>108900</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>99900</v>
+      </c>
+      <c r="AB58" s="3">
         <v>113900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>79900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>99900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>90000</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
       <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
         <v>13000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>13000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>26300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>23100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>23900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>23000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>155400</v>
+      </c>
+      <c r="F59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>8400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4800</v>
       </c>
-      <c r="G59" s="3">
-        <v>153700</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>150200</v>
+      </c>
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>143900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>154100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>485000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>459200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>444000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>411600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>433900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>442800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>467200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>445200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>392000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>419500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>428500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>362400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>357800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>351900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>360100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>283500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>276100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>282600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>335500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>292900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>283800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>309400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>324900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>263700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>479800</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1028500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>912400</v>
+      </c>
+      <c r="F60" s="3">
         <v>955900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1091200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>993100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>976000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>984400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1048700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>921900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>948600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>907500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1024000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>988000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1063600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1011300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1110700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>986100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>937000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>958400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>988900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>819500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>855800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>797100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>855700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>824300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>757000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>756400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>841800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>565000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>532600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>511700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>652400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>572500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>521800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>543900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>622400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>519100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>463800</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1163800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1021800</v>
+      </c>
+      <c r="F61" s="3">
         <v>1105000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1173300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1190200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1010900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1065700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1106500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1288200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1143600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1162500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1099100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1151700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>990800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>990600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>991000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>991400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>691200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>587300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>591500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>691400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>691300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>782000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>790900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>601000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>620900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>620800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>721100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>312600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>312500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>312500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>299300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>302500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>305600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>308800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>312000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>315300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>328500</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>50500</v>
+      </c>
+      <c r="F62" s="3">
         <v>47200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>46400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>45300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>43500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>44500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>45200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>42700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>40800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>38700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>39700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>39700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>149900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>151500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>154100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>156100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>156700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>185100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>186300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>184500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>191400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>180700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>179900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>154200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>93100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>88700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>97900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>50900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>56900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>60400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>60700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>61100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>49300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>56900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>56600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>55400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6421,8 +6719,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6534,8 +6838,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6647,121 +6957,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2283300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1985500</v>
+      </c>
+      <c r="F66" s="3">
         <v>2108700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2311500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2229100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2030900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2095000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2200800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2253200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2133400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2108800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2181400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2210800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2204300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2153300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2255800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2133500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1785000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1730900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1766700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1695400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1738400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1759800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1826500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1579600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1471000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1465900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1660700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>928400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>902100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>884500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1012400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>936000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>876700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>909600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>991000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>889900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>834500</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6801,8 +7123,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6914,8 +7238,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7027,8 +7357,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7140,8 +7476,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7253,121 +7595,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1339600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1390500</v>
+      </c>
+      <c r="F72" s="3">
         <v>1350700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1419600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1414500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1496400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1576200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1583200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1478900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1444100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1403800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1485000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1368500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1280900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1213600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1146800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1040600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1071900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1157400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1151800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1104300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1041500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>981300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>911500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>837200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>784900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>763900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>724000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>613200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>587300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>568400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>538500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>490400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>534300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>578600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>535600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>443600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>480000</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7479,8 +7833,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7592,8 +7952,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7705,121 +8071,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1419200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1453300</v>
+      </c>
+      <c r="F76" s="3">
         <v>1411100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1476600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1467600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1551900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1636400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1651400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1547900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1510900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1477100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1560000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1444200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1351700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1286600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1223500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1119500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1151100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1237200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1229400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1179700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1114800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1054000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>985000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>912100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>859600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>843800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>805300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>694400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>668900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>650200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>623300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>580800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>617100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>659900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>607800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>513000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7931,239 +8309,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45870</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45779</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45506</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45415</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45324</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45142</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45051</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44960</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44771</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44680</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44589</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44407</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44225</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43952</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43679</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43588</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43497</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43315</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43224</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43133</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42951</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42860</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42769</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>73000</v>
+      </c>
+      <c r="F81" s="3">
         <v>53500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>136800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>52800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>89900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>119300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>144800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>64900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>70300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-15000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>167500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>106900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>117600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>125200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>131100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>69500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>60100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>96300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>142200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>111300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>72200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>89000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>98400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>70100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>38300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>60600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>115600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>59500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>39000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>79000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>131300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>22600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>68400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>120500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>45000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8203,121 +8599,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>28200</v>
+      </c>
+      <c r="F83" s="3">
         <v>22100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>21400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>22000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>26900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>18300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>19100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>19200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>20600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>17000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>18800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>18500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>29800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>26100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>28000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>24900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>26500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>23600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>25100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>24100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>25800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>24300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>22800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>22800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>25300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>19000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>27900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>15600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>19400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>11800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>14900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>15200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>17300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>13200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>18000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>16500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8429,8 +8833,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8542,8 +8952,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8655,8 +9071,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8768,8 +9190,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8881,121 +9309,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>313100</v>
+      </c>
+      <c r="F89" s="3">
         <v>225800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>171700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-48600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>240100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>194700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>227300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-92200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>152100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>93000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>130600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-68900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>142600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>111700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>132900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-90000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>78300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>158500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>223600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>95000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>233500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>235000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>94200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>78300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>95100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>138000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>26000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>105400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>120900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>130300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>8100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>84100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>106200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>155000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>15400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>80300</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9035,121 +9475,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-18600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-19300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-19100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-39900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-24100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-20400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-19100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-43800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-35600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-40800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-29300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-67700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-24100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-11900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-56100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-22000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-15700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-10500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-31400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-36100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-23400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-21700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-32900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-32200</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9261,8 +9709,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9374,121 +9828,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-210400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-8300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-23300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-16300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-18400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-19100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-38500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-56500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-40800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-21900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-67700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-25600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-413400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-57800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-21200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-47400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-2100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-31400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-21100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-151800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-28800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-18600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-698700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-26800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-10800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-10900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9528,121 +9994,129 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>37300</v>
+      </c>
+      <c r="F96" s="3">
         <v>37500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>37800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>38500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>36900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>37500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>37500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>37600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>35400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>35400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>35600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>35500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-31300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-31500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-31500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-27800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-28100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-28200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-28400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-27000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-26900</v>
       </c>
       <c r="Z96" s="3">
         <v>-26900</v>
       </c>
       <c r="AA96" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-24100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-24100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-23900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-21200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-21100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-21300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-21400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-18800</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-18900</v>
       </c>
       <c r="AL96" s="3">
         <v>-19000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9754,8 +10228,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9867,8 +10347,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9980,343 +10466,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-193200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-149500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>44600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-244600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-157100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-217500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>114100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-65100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-50200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-106600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>74400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-120500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-99700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-30900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>293300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-152500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-97100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-111100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-143000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-116800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>150600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-40300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-113700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>491800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-38300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-23300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-51900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-88700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-88100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-82900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-32600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-33500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-96300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-64700</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>2600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-3300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>10300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-6200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-2500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-6200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="S101" s="3">
-        <v>2200</v>
       </c>
       <c r="T101" s="3">
         <v>-2500</v>
       </c>
       <c r="U101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="W101" s="3">
         <v>-800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>3600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>4200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>7800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>1800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-152000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>140000</v>
+      </c>
+      <c r="F102" s="3">
         <v>24500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-28200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-21600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>32300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-9700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>45200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-22700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-14200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-43300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>70300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-212700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-129700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>37700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>64200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-46500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>85800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>194100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>91100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-42900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>8500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-36800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-69900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-39200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>38300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>44800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-13600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-90500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>69800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>106300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-114700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-3700</v>
       </c>
     </row>
